--- a/Report/Measuring.xlsx
+++ b/Report/Measuring.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studenthcmusedu-my.sharepoint.com/personal/22127275_student_hcmus_edu_vn/Documents/Programming/DSA/Lab3_Sorting/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1280" documentId="8_{DA9940A0-0571-4566-AD57-949AA40DBC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{54FB3A1E-A977-4FDB-A671-C96B318C6FCE}"/>
+  <xr:revisionPtr revIDLastSave="1356" documentId="8_{DA9940A0-0571-4566-AD57-949AA40DBC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D32FEB1F-43D8-4FA4-AFB4-F77A0C53C2E9}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00802968-0738-4320-9C05-4460BE5590E3}"/>
   </bookViews>
@@ -196,7 +196,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="8" x14ac:knownFonts="1">
+  <fonts count="9" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,8 +258,15 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="14"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="7">
+  <fills count="9">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -294,6 +301,18 @@
       <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFDDEBF7"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFF2CC"/>
+        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -346,7 +365,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="15">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -377,6 +396,15 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -3004,17 +3032,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="N4:O5"/>
+    <mergeCell ref="P4:Q5"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:U5"/>
+    <mergeCell ref="V4:W5"/>
     <mergeCell ref="L4:M5"/>
     <mergeCell ref="B4:C5"/>
     <mergeCell ref="D4:E5"/>
     <mergeCell ref="F4:G5"/>
     <mergeCell ref="H4:I5"/>
     <mergeCell ref="J4:K5"/>
-    <mergeCell ref="N4:O5"/>
-    <mergeCell ref="P4:Q5"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:U5"/>
-    <mergeCell ref="V4:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3026,14 +3054,17 @@
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A4:M68"/>
+  <dimension ref="A4:R68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
     <col min="2" max="13" width="20.85546875" customWidth="1"/>
+    <col min="15" max="15" width="15.5703125" customWidth="1"/>
+    <col min="16" max="16" width="21.28515625" customWidth="1"/>
+    <col min="18" max="18" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:18" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="10" t="s">
         <v>46</v>
       </c>
@@ -3050,7 +3081,7 @@
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
     </row>
-    <row r="5" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>43</v>
       </c>
@@ -3079,7 +3110,7 @@
       </c>
       <c r="M5" s="11"/>
     </row>
-    <row r="6" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>45</v>
       </c>
@@ -3120,7 +3151,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>40</v>
       </c>
@@ -3148,20 +3179,32 @@
       <c r="I7" s="2">
         <v>10000066045</v>
       </c>
-      <c r="J7" s="8">
+      <c r="J7" s="12">
+        <v>510117</v>
+      </c>
+      <c r="K7" s="13">
+        <v>90000586312</v>
+      </c>
+      <c r="L7" s="14">
+        <v>1486030</v>
+      </c>
+      <c r="M7" s="2">
+        <v>250000835165</v>
+      </c>
+      <c r="O7" s="8">
         <v>513952</v>
       </c>
-      <c r="K7" s="2">
+      <c r="P7" s="2">
         <v>90000391152</v>
       </c>
-      <c r="L7" s="8">
+      <c r="Q7" s="8">
         <v>1436930</v>
       </c>
-      <c r="M7" s="2">
+      <c r="R7" s="2">
         <v>249999489560</v>
       </c>
     </row>
-    <row r="8" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>42</v>
       </c>
@@ -3189,20 +3232,32 @@
       <c r="I8" s="2">
         <v>332768</v>
       </c>
-      <c r="J8" s="8">
-        <v>10.702400000000001</v>
-      </c>
-      <c r="K8" s="2">
+      <c r="J8" s="12">
+        <v>6.1920999999999999</v>
+      </c>
+      <c r="K8" s="13">
         <v>932768</v>
       </c>
       <c r="L8" s="8">
-        <v>9.0576000000000008</v>
+        <v>10.4316</v>
       </c>
       <c r="M8" s="2">
         <v>1532768</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O8" s="8">
+        <v>10.702400000000001</v>
+      </c>
+      <c r="P8" s="2">
+        <v>932768</v>
+      </c>
+      <c r="Q8" s="8">
+        <v>9.0576000000000008</v>
+      </c>
+      <c r="R8" s="2">
+        <v>1532768</v>
+      </c>
+    </row>
+    <row r="9" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>41</v>
       </c>
@@ -3230,20 +3285,32 @@
       <c r="I9" s="2">
         <v>1077495</v>
       </c>
-      <c r="J9" s="8">
+      <c r="J9" s="12">
+        <v>42.047699999999999</v>
+      </c>
+      <c r="K9" s="13">
+        <v>3536437</v>
+      </c>
+      <c r="L9" s="8">
+        <v>64.264799999999994</v>
+      </c>
+      <c r="M9" s="2">
+        <v>5805419</v>
+      </c>
+      <c r="O9" s="8">
         <v>26.746200000000002</v>
       </c>
-      <c r="K9" s="2">
+      <c r="P9" s="2">
         <v>3562347</v>
       </c>
-      <c r="L9" s="8">
+      <c r="Q9" s="8">
         <v>49.616</v>
       </c>
-      <c r="M9" s="2">
+      <c r="R9" s="2">
         <v>6073735</v>
       </c>
     </row>
-    <row r="10" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>39</v>
       </c>
@@ -3271,20 +3338,32 @@
       <c r="I10" s="2">
         <v>4829292</v>
       </c>
-      <c r="J10" s="8">
+      <c r="J10" s="12">
+        <v>120.364</v>
+      </c>
+      <c r="K10" s="13">
+        <v>15900654</v>
+      </c>
+      <c r="L10" s="8">
+        <v>230.929</v>
+      </c>
+      <c r="M10" s="2">
+        <v>27594993</v>
+      </c>
+      <c r="O10" s="8">
         <v>119.447</v>
       </c>
-      <c r="K10" s="2">
+      <c r="P10" s="2">
         <v>15902916</v>
       </c>
-      <c r="L10" s="8">
+      <c r="Q10" s="8">
         <v>196.636</v>
       </c>
-      <c r="M10" s="2">
+      <c r="R10" s="2">
         <v>27594312</v>
       </c>
     </row>
-    <row r="11" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
@@ -3312,20 +3391,32 @@
       <c r="I11" s="2">
         <v>4996899593</v>
       </c>
-      <c r="J11" s="8">
+      <c r="J11" s="12">
+        <v>136502</v>
+      </c>
+      <c r="K11" s="13">
+        <v>44968615218</v>
+      </c>
+      <c r="L11" s="8">
+        <v>383201</v>
+      </c>
+      <c r="M11" s="2">
+        <v>125169489447</v>
+      </c>
+      <c r="O11" s="8">
         <v>137411</v>
       </c>
-      <c r="K11" s="2">
+      <c r="P11" s="2">
         <v>44960162813</v>
       </c>
-      <c r="L11" s="8">
+      <c r="Q11" s="8">
         <v>359524</v>
       </c>
-      <c r="M11" s="2">
+      <c r="R11" s="2">
         <v>125068299550</v>
       </c>
     </row>
-    <row r="12" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>37</v>
       </c>
@@ -3353,20 +3444,32 @@
       <c r="I12" s="2">
         <v>6233721</v>
       </c>
-      <c r="J12" s="8">
+      <c r="J12" s="12">
+        <v>114.464</v>
+      </c>
+      <c r="K12" s="13">
+        <v>20347405</v>
+      </c>
+      <c r="L12" s="8">
+        <v>179.22399999999999</v>
+      </c>
+      <c r="M12" s="2">
+        <v>35178923</v>
+      </c>
+      <c r="O12" s="8">
         <v>102.27500000000001</v>
       </c>
-      <c r="K12" s="2">
+      <c r="P12" s="2">
         <v>20346547</v>
       </c>
-      <c r="L12" s="8">
+      <c r="Q12" s="8">
         <v>190.119</v>
       </c>
-      <c r="M12" s="2">
+      <c r="R12" s="2">
         <v>35178039</v>
       </c>
     </row>
-    <row r="13" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>36</v>
       </c>
@@ -3394,20 +3497,32 @@
       <c r="I13" s="2">
         <v>3863131</v>
       </c>
-      <c r="J13" s="8">
+      <c r="J13" s="12">
+        <v>63.337699999999998</v>
+      </c>
+      <c r="K13" s="13">
+        <v>13761099</v>
+      </c>
+      <c r="L13" s="8">
+        <v>125.27</v>
+      </c>
+      <c r="M13" s="2">
+        <v>25492171</v>
+      </c>
+      <c r="O13" s="8">
         <v>72.512200000000007</v>
       </c>
-      <c r="K13" s="2">
+      <c r="P13" s="2">
         <v>13711223</v>
       </c>
-      <c r="L13" s="8">
+      <c r="Q13" s="8">
         <v>114.542</v>
       </c>
-      <c r="M13" s="2">
+      <c r="R13" s="2">
         <v>25623393</v>
       </c>
     </row>
-    <row r="14" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>35</v>
       </c>
@@ -3435,20 +3550,32 @@
       <c r="I14" s="2">
         <v>1300120</v>
       </c>
-      <c r="J14" s="8">
-        <v>86.862899999999996</v>
-      </c>
-      <c r="K14" s="2">
+      <c r="J14" s="12">
+        <v>79.879900000000006</v>
+      </c>
+      <c r="K14" s="13">
         <v>3900120</v>
       </c>
       <c r="L14" s="8">
-        <v>139.51599999999999</v>
+        <v>133.28899999999999</v>
       </c>
       <c r="M14" s="2">
         <v>6500120</v>
       </c>
-    </row>
-    <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="O14" s="8">
+        <v>86.862899999999996</v>
+      </c>
+      <c r="P14" s="2">
+        <v>3900120</v>
+      </c>
+      <c r="Q14" s="8">
+        <v>139.51599999999999</v>
+      </c>
+      <c r="R14" s="2">
+        <v>6500120</v>
+      </c>
+    </row>
+    <row r="15" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>34</v>
       </c>
@@ -3476,20 +3603,30 @@
       <c r="I15" s="2">
         <v>10000199998</v>
       </c>
-      <c r="J15" s="8">
+      <c r="J15" s="12">
+        <v>225883</v>
+      </c>
+      <c r="K15" s="13">
+        <v>90000599998</v>
+      </c>
+      <c r="L15" s="8">
+        <v>617310</v>
+      </c>
+      <c r="M15" s="2"/>
+      <c r="O15" s="8">
         <v>215658</v>
       </c>
-      <c r="K15" s="2">
+      <c r="P15" s="2">
         <v>90000599998</v>
       </c>
-      <c r="L15" s="8">
+      <c r="Q15" s="8">
         <v>598300</v>
       </c>
-      <c r="M15" s="2">
+      <c r="R15" s="2">
         <v>250000999998</v>
       </c>
     </row>
-    <row r="16" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>32</v>
       </c>
@@ -3518,19 +3655,27 @@
         <v>7484826744</v>
       </c>
       <c r="J16" s="8">
+        <v>397273</v>
+      </c>
+      <c r="K16" s="2">
+        <v>67502549944</v>
+      </c>
+      <c r="L16" s="8"/>
+      <c r="M16" s="2"/>
+      <c r="O16" s="8">
         <v>382225</v>
       </c>
-      <c r="K16" s="2">
+      <c r="P16" s="2">
         <v>67311957498</v>
       </c>
-      <c r="L16" s="8">
+      <c r="Q16" s="8">
         <v>1038750</v>
       </c>
-      <c r="M16" s="2">
+      <c r="R16" s="2">
         <v>187697095158</v>
       </c>
     </row>
-    <row r="17" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
@@ -3559,19 +3704,27 @@
         <v>8383847</v>
       </c>
       <c r="J17" s="8">
+        <v>123.712</v>
+      </c>
+      <c r="K17" s="2">
+        <v>31952285</v>
+      </c>
+      <c r="L17" s="8"/>
+      <c r="M17" s="2"/>
+      <c r="O17" s="8">
         <v>120.20099999999999</v>
       </c>
-      <c r="K17" s="2">
+      <c r="P17" s="2">
         <v>30918022</v>
       </c>
-      <c r="L17" s="8">
+      <c r="Q17" s="8">
         <v>222.84299999999999</v>
       </c>
-      <c r="M17" s="2">
+      <c r="R17" s="2">
         <v>59976940</v>
       </c>
     </row>
-    <row r="21" spans="1:13" ht="46.5" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:18" ht="46.5" x14ac:dyDescent="0.25">
       <c r="A21" s="10" t="s">
         <v>48</v>
       </c>
@@ -3588,7 +3741,7 @@
       <c r="L21" s="10"/>
       <c r="M21" s="10"/>
     </row>
-    <row r="22" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
@@ -3617,7 +3770,7 @@
       </c>
       <c r="M22" s="11"/>
     </row>
-    <row r="23" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>45</v>
       </c>
@@ -3658,7 +3811,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>40</v>
       </c>
@@ -3699,7 +3852,7 @@
         <v>11842359776</v>
       </c>
     </row>
-    <row r="25" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>42</v>
       </c>
@@ -3740,7 +3893,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="26" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>41</v>
       </c>
@@ -3781,7 +3934,7 @@
         <v>4175025</v>
       </c>
     </row>
-    <row r="27" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>39</v>
       </c>
@@ -3822,7 +3975,7 @@
         <v>28268334</v>
       </c>
     </row>
-    <row r="28" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>38</v>
       </c>
@@ -3863,7 +4016,7 @@
         <v>1690026</v>
       </c>
     </row>
-    <row r="29" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>37</v>
       </c>
@@ -3904,7 +4057,7 @@
         <v>26806893</v>
       </c>
     </row>
-    <row r="30" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>36</v>
       </c>
@@ -3945,7 +4098,7 @@
         <v>18905233</v>
       </c>
     </row>
-    <row r="31" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>35</v>
       </c>
@@ -3986,7 +4139,7 @@
         <v>7500143</v>
       </c>
     </row>
-    <row r="32" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
@@ -5187,20 +5340,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A55:M55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A21:M21"/>
     <mergeCell ref="B22:C22"/>
@@ -5215,6 +5354,20 @@
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="A55:M55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="L56:M56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Report/Measuring.xlsx
+++ b/Report/Measuring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studenthcmusedu-my.sharepoint.com/personal/22127275_student_hcmus_edu_vn/Documents/Programming/DSA/Lab3_Sorting/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1356" documentId="8_{DA9940A0-0571-4566-AD57-949AA40DBC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D32FEB1F-43D8-4FA4-AFB4-F77A0C53C2E9}"/>
+  <xr:revisionPtr revIDLastSave="1403" documentId="8_{DA9940A0-0571-4566-AD57-949AA40DBC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F882A60F-7BB8-4345-A79A-BE041592BD31}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00802968-0738-4320-9C05-4460BE5590E3}"/>
+    <workbookView xWindow="8925" yWindow="585" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00802968-0738-4320-9C05-4460BE5590E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Huy" sheetId="1" r:id="rId1"/>
@@ -389,6 +389,15 @@
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="3" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="11" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -396,15 +405,6 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="3" fontId="3" fillId="5" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -735,74 +735,74 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B4" s="9" t="s">
+      <c r="B4" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="9"/>
-      <c r="D4" s="9" t="s">
+      <c r="C4" s="12"/>
+      <c r="D4" s="12" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="9"/>
-      <c r="F4" s="9" t="s">
+      <c r="E4" s="12"/>
+      <c r="F4" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="9"/>
-      <c r="H4" s="9" t="s">
+      <c r="G4" s="12"/>
+      <c r="H4" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="9"/>
-      <c r="J4" s="9" t="s">
+      <c r="I4" s="12"/>
+      <c r="J4" s="12" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="9"/>
-      <c r="L4" s="9" t="s">
+      <c r="K4" s="12"/>
+      <c r="L4" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="9"/>
-      <c r="N4" s="9" t="s">
+      <c r="M4" s="12"/>
+      <c r="N4" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="O4" s="9"/>
-      <c r="P4" s="9" t="s">
+      <c r="O4" s="12"/>
+      <c r="P4" s="12" t="s">
         <v>35</v>
       </c>
-      <c r="Q4" s="9"/>
-      <c r="R4" s="9" t="s">
+      <c r="Q4" s="12"/>
+      <c r="R4" s="12" t="s">
         <v>34</v>
       </c>
-      <c r="S4" s="9"/>
-      <c r="T4" s="9" t="s">
+      <c r="S4" s="12"/>
+      <c r="T4" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="U4" s="9"/>
-      <c r="V4" s="9" t="s">
+      <c r="U4" s="12"/>
+      <c r="V4" s="12" t="s">
         <v>33</v>
       </c>
-      <c r="W4" s="9"/>
+      <c r="W4" s="12"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B5" s="9"/>
-      <c r="C5" s="9"/>
-      <c r="D5" s="9"/>
-      <c r="E5" s="9"/>
-      <c r="F5" s="9"/>
-      <c r="G5" s="9"/>
-      <c r="H5" s="9"/>
-      <c r="I5" s="9"/>
-      <c r="J5" s="9"/>
-      <c r="K5" s="9"/>
-      <c r="L5" s="9"/>
-      <c r="M5" s="9"/>
-      <c r="N5" s="9"/>
-      <c r="O5" s="9"/>
-      <c r="P5" s="9"/>
-      <c r="Q5" s="9"/>
-      <c r="R5" s="9"/>
-      <c r="S5" s="9"/>
-      <c r="T5" s="9"/>
-      <c r="U5" s="9"/>
-      <c r="V5" s="9"/>
-      <c r="W5" s="9"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="12"/>
+      <c r="D5" s="12"/>
+      <c r="E5" s="12"/>
+      <c r="F5" s="12"/>
+      <c r="G5" s="12"/>
+      <c r="H5" s="12"/>
+      <c r="I5" s="12"/>
+      <c r="J5" s="12"/>
+      <c r="K5" s="12"/>
+      <c r="L5" s="12"/>
+      <c r="M5" s="12"/>
+      <c r="N5" s="12"/>
+      <c r="O5" s="12"/>
+      <c r="P5" s="12"/>
+      <c r="Q5" s="12"/>
+      <c r="R5" s="12"/>
+      <c r="S5" s="12"/>
+      <c r="T5" s="12"/>
+      <c r="U5" s="12"/>
+      <c r="V5" s="12"/>
+      <c r="W5" s="12"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -3032,17 +3032,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
-    <mergeCell ref="N4:O5"/>
-    <mergeCell ref="P4:Q5"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:U5"/>
-    <mergeCell ref="V4:W5"/>
     <mergeCell ref="L4:M5"/>
     <mergeCell ref="B4:C5"/>
     <mergeCell ref="D4:E5"/>
     <mergeCell ref="F4:G5"/>
     <mergeCell ref="H4:I5"/>
     <mergeCell ref="J4:K5"/>
+    <mergeCell ref="N4:O5"/>
+    <mergeCell ref="P4:Q5"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:U5"/>
+    <mergeCell ref="V4:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3065,50 +3065,50 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:18" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="10" t="s">
+      <c r="A4" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="10"/>
-      <c r="C4" s="10"/>
-      <c r="D4" s="10"/>
-      <c r="E4" s="10"/>
-      <c r="F4" s="10"/>
-      <c r="G4" s="10"/>
-      <c r="H4" s="10"/>
-      <c r="I4" s="10"/>
-      <c r="J4" s="10"/>
-      <c r="K4" s="10"/>
-      <c r="L4" s="10"/>
-      <c r="M4" s="10"/>
+      <c r="B4" s="13"/>
+      <c r="C4" s="13"/>
+      <c r="D4" s="13"/>
+      <c r="E4" s="13"/>
+      <c r="F4" s="13"/>
+      <c r="G4" s="13"/>
+      <c r="H4" s="13"/>
+      <c r="I4" s="13"/>
+      <c r="J4" s="13"/>
+      <c r="K4" s="13"/>
+      <c r="L4" s="13"/>
+      <c r="M4" s="13"/>
     </row>
     <row r="5" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="11">
+      <c r="B5" s="14">
         <v>10000</v>
       </c>
-      <c r="C5" s="11"/>
-      <c r="D5" s="11">
+      <c r="C5" s="14"/>
+      <c r="D5" s="14">
         <v>30000</v>
       </c>
-      <c r="E5" s="11"/>
-      <c r="F5" s="11">
+      <c r="E5" s="14"/>
+      <c r="F5" s="14">
         <v>50000</v>
       </c>
-      <c r="G5" s="11"/>
-      <c r="H5" s="11">
+      <c r="G5" s="14"/>
+      <c r="H5" s="14">
         <v>100000</v>
       </c>
-      <c r="I5" s="11"/>
-      <c r="J5" s="11">
+      <c r="I5" s="14"/>
+      <c r="J5" s="14">
         <v>300000</v>
       </c>
-      <c r="K5" s="11"/>
-      <c r="L5" s="11">
+      <c r="K5" s="14"/>
+      <c r="L5" s="14">
         <v>500000</v>
       </c>
-      <c r="M5" s="11"/>
+      <c r="M5" s="14"/>
     </row>
     <row r="6" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
@@ -3179,18 +3179,10 @@
       <c r="I7" s="2">
         <v>10000066045</v>
       </c>
-      <c r="J7" s="12">
-        <v>510117</v>
-      </c>
-      <c r="K7" s="13">
-        <v>90000586312</v>
-      </c>
-      <c r="L7" s="14">
-        <v>1486030</v>
-      </c>
-      <c r="M7" s="2">
-        <v>250000835165</v>
-      </c>
+      <c r="J7" s="9"/>
+      <c r="K7" s="10"/>
+      <c r="L7" s="11"/>
+      <c r="M7" s="2"/>
       <c r="O7" s="8">
         <v>513952</v>
       </c>
@@ -3232,14 +3224,14 @@
       <c r="I8" s="2">
         <v>332768</v>
       </c>
-      <c r="J8" s="12">
-        <v>6.1920999999999999</v>
-      </c>
-      <c r="K8" s="13">
+      <c r="J8" s="9">
+        <v>16.330200000000001</v>
+      </c>
+      <c r="K8" s="10">
         <v>932768</v>
       </c>
       <c r="L8" s="8">
-        <v>10.4316</v>
+        <v>27.058800000000002</v>
       </c>
       <c r="M8" s="2">
         <v>1532768</v>
@@ -3285,17 +3277,17 @@
       <c r="I9" s="2">
         <v>1077495</v>
       </c>
-      <c r="J9" s="12">
-        <v>42.047699999999999</v>
-      </c>
-      <c r="K9" s="13">
-        <v>3536437</v>
+      <c r="J9" s="9">
+        <v>29.6447</v>
+      </c>
+      <c r="K9" s="10">
+        <v>3572703</v>
       </c>
       <c r="L9" s="8">
-        <v>64.264799999999994</v>
+        <v>46.386699999999998</v>
       </c>
       <c r="M9" s="2">
-        <v>5805419</v>
+        <v>5759747</v>
       </c>
       <c r="O9" s="8">
         <v>26.746200000000002</v>
@@ -3338,17 +3330,17 @@
       <c r="I10" s="2">
         <v>4829292</v>
       </c>
-      <c r="J10" s="12">
-        <v>120.364</v>
-      </c>
-      <c r="K10" s="13">
-        <v>15900654</v>
+      <c r="J10" s="9">
+        <v>249.9</v>
+      </c>
+      <c r="K10" s="10">
+        <v>15902205</v>
       </c>
       <c r="L10" s="8">
-        <v>230.929</v>
+        <v>399.78399999999999</v>
       </c>
       <c r="M10" s="2">
-        <v>27594993</v>
+        <v>27595962</v>
       </c>
       <c r="O10" s="8">
         <v>119.447</v>
@@ -3391,18 +3383,10 @@
       <c r="I11" s="2">
         <v>4996899593</v>
       </c>
-      <c r="J11" s="12">
-        <v>136502</v>
-      </c>
-      <c r="K11" s="13">
-        <v>44968615218</v>
-      </c>
-      <c r="L11" s="8">
-        <v>383201</v>
-      </c>
-      <c r="M11" s="2">
-        <v>125169489447</v>
-      </c>
+      <c r="J11" s="9"/>
+      <c r="K11" s="10"/>
+      <c r="L11" s="8"/>
+      <c r="M11" s="2"/>
       <c r="O11" s="8">
         <v>137411</v>
       </c>
@@ -3444,17 +3428,17 @@
       <c r="I12" s="2">
         <v>6233721</v>
       </c>
-      <c r="J12" s="12">
-        <v>114.464</v>
-      </c>
-      <c r="K12" s="13">
-        <v>20347405</v>
+      <c r="J12" s="9">
+        <v>156.96199999999999</v>
+      </c>
+      <c r="K12" s="10">
+        <v>20346836</v>
       </c>
       <c r="L12" s="8">
-        <v>179.22399999999999</v>
+        <v>303.06900000000002</v>
       </c>
       <c r="M12" s="2">
-        <v>35178923</v>
+        <v>35177908</v>
       </c>
       <c r="O12" s="8">
         <v>102.27500000000001</v>
@@ -3497,17 +3481,17 @@
       <c r="I13" s="2">
         <v>3863131</v>
       </c>
-      <c r="J13" s="12">
-        <v>63.337699999999998</v>
-      </c>
-      <c r="K13" s="13">
-        <v>13761099</v>
+      <c r="J13" s="9">
+        <v>106.68899999999999</v>
+      </c>
+      <c r="K13" s="10">
+        <v>14420831</v>
       </c>
       <c r="L13" s="8">
-        <v>125.27</v>
+        <v>210.13800000000001</v>
       </c>
       <c r="M13" s="2">
-        <v>25492171</v>
+        <v>27736587</v>
       </c>
       <c r="O13" s="8">
         <v>72.512200000000007</v>
@@ -3550,14 +3534,14 @@
       <c r="I14" s="2">
         <v>1300120</v>
       </c>
-      <c r="J14" s="12">
-        <v>79.879900000000006</v>
-      </c>
-      <c r="K14" s="13">
+      <c r="J14" s="9">
+        <v>222.79400000000001</v>
+      </c>
+      <c r="K14" s="10">
         <v>3900120</v>
       </c>
       <c r="L14" s="8">
-        <v>133.28899999999999</v>
+        <v>362.94099999999997</v>
       </c>
       <c r="M14" s="2">
         <v>6500120</v>
@@ -3603,15 +3587,9 @@
       <c r="I15" s="2">
         <v>10000199998</v>
       </c>
-      <c r="J15" s="12">
-        <v>225883</v>
-      </c>
-      <c r="K15" s="13">
-        <v>90000599998</v>
-      </c>
-      <c r="L15" s="8">
-        <v>617310</v>
-      </c>
+      <c r="J15" s="9"/>
+      <c r="K15" s="10"/>
+      <c r="L15" s="8"/>
       <c r="M15" s="2"/>
       <c r="O15" s="8">
         <v>215658</v>
@@ -3654,12 +3632,8 @@
       <c r="I16" s="2">
         <v>7484826744</v>
       </c>
-      <c r="J16" s="8">
-        <v>397273</v>
-      </c>
-      <c r="K16" s="2">
-        <v>67502549944</v>
-      </c>
+      <c r="J16" s="8"/>
+      <c r="K16" s="2"/>
       <c r="L16" s="8"/>
       <c r="M16" s="2"/>
       <c r="O16" s="8">
@@ -3704,13 +3678,17 @@
         <v>8383847</v>
       </c>
       <c r="J17" s="8">
-        <v>123.712</v>
+        <v>45.911999999999999</v>
       </c>
       <c r="K17" s="2">
-        <v>31952285</v>
-      </c>
-      <c r="L17" s="8"/>
-      <c r="M17" s="2"/>
+        <v>31948207</v>
+      </c>
+      <c r="L17" s="8">
+        <v>113.16800000000001</v>
+      </c>
+      <c r="M17" s="2">
+        <v>59722045</v>
+      </c>
       <c r="O17" s="8">
         <v>120.20099999999999</v>
       </c>
@@ -3725,50 +3703,50 @@
       </c>
     </row>
     <row r="21" spans="1:18" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="10" t="s">
+      <c r="A21" s="13" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="10"/>
-      <c r="C21" s="10"/>
-      <c r="D21" s="10"/>
-      <c r="E21" s="10"/>
-      <c r="F21" s="10"/>
-      <c r="G21" s="10"/>
-      <c r="H21" s="10"/>
-      <c r="I21" s="10"/>
-      <c r="J21" s="10"/>
-      <c r="K21" s="10"/>
-      <c r="L21" s="10"/>
-      <c r="M21" s="10"/>
+      <c r="B21" s="13"/>
+      <c r="C21" s="13"/>
+      <c r="D21" s="13"/>
+      <c r="E21" s="13"/>
+      <c r="F21" s="13"/>
+      <c r="G21" s="13"/>
+      <c r="H21" s="13"/>
+      <c r="I21" s="13"/>
+      <c r="J21" s="13"/>
+      <c r="K21" s="13"/>
+      <c r="L21" s="13"/>
+      <c r="M21" s="13"/>
     </row>
     <row r="22" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="11">
+      <c r="B22" s="14">
         <v>10000</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11">
+      <c r="C22" s="14"/>
+      <c r="D22" s="14">
         <v>30000</v>
       </c>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11">
+      <c r="E22" s="14"/>
+      <c r="F22" s="14">
         <v>50000</v>
       </c>
-      <c r="G22" s="11"/>
-      <c r="H22" s="11">
+      <c r="G22" s="14"/>
+      <c r="H22" s="14">
         <v>100000</v>
       </c>
-      <c r="I22" s="11"/>
-      <c r="J22" s="11">
+      <c r="I22" s="14"/>
+      <c r="J22" s="14">
         <v>300000</v>
       </c>
-      <c r="K22" s="11"/>
-      <c r="L22" s="11">
+      <c r="K22" s="14"/>
+      <c r="L22" s="14">
         <v>500000</v>
       </c>
-      <c r="M22" s="11"/>
+      <c r="M22" s="14"/>
     </row>
     <row r="23" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
@@ -3839,16 +3817,20 @@
       <c r="I24" s="2">
         <v>3713613057</v>
       </c>
-      <c r="J24" s="8">
+      <c r="J24" s="8"/>
+      <c r="K24" s="2"/>
+      <c r="L24" s="8"/>
+      <c r="M24" s="2"/>
+      <c r="O24" s="8">
         <v>40094</v>
       </c>
-      <c r="K24" s="2">
+      <c r="P24" s="2">
         <v>16565019901</v>
       </c>
-      <c r="L24" s="8">
+      <c r="Q24" s="8">
         <v>27860.6</v>
       </c>
-      <c r="M24" s="2">
+      <c r="R24" s="2">
         <v>11842359776</v>
       </c>
     </row>
@@ -3881,15 +3863,23 @@
         <v>400000</v>
       </c>
       <c r="J25" s="8">
-        <v>10.995699999999999</v>
+        <v>25.383600000000001</v>
       </c>
       <c r="K25" s="2">
         <v>1200000</v>
       </c>
-      <c r="L25" s="8">
+      <c r="L25" s="8"/>
+      <c r="M25" s="2"/>
+      <c r="O25" s="8">
+        <v>10.995699999999999</v>
+      </c>
+      <c r="P25" s="2">
+        <v>1200000</v>
+      </c>
+      <c r="Q25" s="8">
         <v>15.128299999999999</v>
       </c>
-      <c r="M25" s="2">
+      <c r="R25" s="2">
         <v>2000000</v>
       </c>
     </row>
@@ -3922,15 +3912,23 @@
         <v>835023</v>
       </c>
       <c r="J26" s="8">
+        <v>26.213999999999999</v>
+      </c>
+      <c r="K26" s="2">
+        <v>2505033</v>
+      </c>
+      <c r="L26" s="8"/>
+      <c r="M26" s="2"/>
+      <c r="O26" s="8">
         <v>10.401199999999999</v>
       </c>
-      <c r="K26" s="2">
+      <c r="P26" s="2">
         <v>2505034</v>
       </c>
-      <c r="L26" s="8">
+      <c r="Q26" s="8">
         <v>16.7559</v>
       </c>
-      <c r="M26" s="2">
+      <c r="R26" s="2">
         <v>4175025</v>
       </c>
     </row>
@@ -3962,16 +3960,20 @@
       <c r="I27" s="2">
         <v>4969320</v>
       </c>
-      <c r="J27" s="8">
+      <c r="J27" s="8"/>
+      <c r="K27" s="2"/>
+      <c r="L27" s="8"/>
+      <c r="M27" s="2"/>
+      <c r="O27" s="8">
         <v>102.003</v>
       </c>
-      <c r="K27" s="2">
+      <c r="P27" s="2">
         <v>16322175</v>
       </c>
-      <c r="L27" s="8">
+      <c r="Q27" s="8">
         <v>170.22499999999999</v>
       </c>
-      <c r="M27" s="2">
+      <c r="R27" s="2">
         <v>28268334</v>
       </c>
     </row>
@@ -4003,16 +4005,20 @@
       <c r="I28" s="2">
         <v>743862</v>
       </c>
-      <c r="J28" s="8">
+      <c r="J28" s="8"/>
+      <c r="K28" s="2"/>
+      <c r="L28" s="8"/>
+      <c r="M28" s="2"/>
+      <c r="O28" s="8">
         <v>4.3433000000000002</v>
       </c>
-      <c r="K28" s="2">
+      <c r="P28" s="2">
         <v>1362474</v>
       </c>
-      <c r="L28" s="8">
+      <c r="Q28" s="8">
         <v>4.9542000000000002</v>
       </c>
-      <c r="M28" s="2">
+      <c r="R28" s="2">
         <v>1690026</v>
       </c>
     </row>
@@ -4044,16 +4050,20 @@
       <c r="I29" s="2">
         <v>4900830</v>
       </c>
-      <c r="J29" s="8">
+      <c r="J29" s="8"/>
+      <c r="K29" s="2"/>
+      <c r="L29" s="8"/>
+      <c r="M29" s="2"/>
+      <c r="O29" s="8">
         <v>67.150499999999994</v>
       </c>
-      <c r="K29" s="2">
+      <c r="P29" s="2">
         <v>15650920</v>
       </c>
-      <c r="L29" s="8">
+      <c r="Q29" s="8">
         <v>121.15</v>
       </c>
-      <c r="M29" s="2">
+      <c r="R29" s="2">
         <v>26806893</v>
       </c>
     </row>
@@ -4085,16 +4095,20 @@
       <c r="I30" s="2">
         <v>3579619</v>
       </c>
-      <c r="J30" s="8">
+      <c r="J30" s="8"/>
+      <c r="K30" s="2"/>
+      <c r="L30" s="8"/>
+      <c r="M30" s="2"/>
+      <c r="O30" s="8">
         <v>42.811399999999999</v>
       </c>
-      <c r="K30" s="2">
+      <c r="P30" s="2">
         <v>11069303</v>
       </c>
-      <c r="L30" s="8">
+      <c r="Q30" s="8">
         <v>77.176599999999993</v>
       </c>
-      <c r="M30" s="2">
+      <c r="R30" s="2">
         <v>18905233</v>
       </c>
     </row>
@@ -4126,16 +4140,20 @@
       <c r="I31" s="2">
         <v>1300120</v>
       </c>
-      <c r="J31" s="8">
+      <c r="J31" s="8"/>
+      <c r="K31" s="2"/>
+      <c r="L31" s="8"/>
+      <c r="M31" s="2"/>
+      <c r="O31" s="8">
         <v>83.856399999999994</v>
       </c>
-      <c r="K31" s="2">
+      <c r="P31" s="2">
         <v>4500143</v>
       </c>
-      <c r="L31" s="8">
+      <c r="Q31" s="8">
         <v>144.67400000000001</v>
       </c>
-      <c r="M31" s="2">
+      <c r="R31" s="2">
         <v>7500143</v>
       </c>
     </row>
@@ -4167,20 +4185,24 @@
       <c r="I32" s="2">
         <v>10000199998</v>
       </c>
-      <c r="J32" s="8">
+      <c r="J32" s="8"/>
+      <c r="K32" s="2"/>
+      <c r="L32" s="8"/>
+      <c r="M32" s="2"/>
+      <c r="O32" s="8">
         <v>214278</v>
       </c>
-      <c r="K32" s="2">
+      <c r="P32" s="2">
         <v>90000599998</v>
       </c>
-      <c r="L32" s="8">
+      <c r="Q32" s="8">
         <v>582223</v>
       </c>
-      <c r="M32" s="2">
+      <c r="R32" s="2">
         <v>250000999998</v>
       </c>
     </row>
-    <row r="33" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>32</v>
       </c>
@@ -4208,20 +4230,24 @@
       <c r="I33" s="2">
         <v>2799818</v>
       </c>
-      <c r="J33" s="8">
+      <c r="J33" s="8"/>
+      <c r="K33" s="2"/>
+      <c r="L33" s="8"/>
+      <c r="M33" s="2"/>
+      <c r="O33" s="8">
         <v>30.553000000000001</v>
       </c>
-      <c r="K33" s="2">
+      <c r="P33" s="2">
         <v>11999620</v>
       </c>
-      <c r="L33" s="8">
+      <c r="Q33" s="8">
         <v>51.583199999999998</v>
       </c>
-      <c r="M33" s="2">
+      <c r="R33" s="2">
         <v>17999694</v>
       </c>
     </row>
-    <row r="34" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>33</v>
       </c>
@@ -4249,66 +4275,70 @@
       <c r="I34" s="2">
         <v>3062589</v>
       </c>
-      <c r="J34" s="8">
+      <c r="J34" s="8"/>
+      <c r="K34" s="2"/>
+      <c r="L34" s="8"/>
+      <c r="M34" s="2"/>
+      <c r="O34" s="8">
         <v>26.707100000000001</v>
       </c>
-      <c r="K34" s="2">
+      <c r="P34" s="2">
         <v>9816956</v>
       </c>
-      <c r="L34" s="8">
+      <c r="Q34" s="8">
         <v>47.722900000000003</v>
       </c>
-      <c r="M34" s="2">
+      <c r="R34" s="2">
         <v>16954347</v>
       </c>
     </row>
-    <row r="38" spans="1:13" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="10" t="s">
+    <row r="38" spans="1:18" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="13" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="10"/>
-      <c r="C38" s="10"/>
-      <c r="D38" s="10"/>
-      <c r="E38" s="10"/>
-      <c r="F38" s="10"/>
-      <c r="G38" s="10"/>
-      <c r="H38" s="10"/>
-      <c r="I38" s="10"/>
-      <c r="J38" s="10"/>
-      <c r="K38" s="10"/>
-      <c r="L38" s="10"/>
-      <c r="M38" s="10"/>
-    </row>
-    <row r="39" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B38" s="13"/>
+      <c r="C38" s="13"/>
+      <c r="D38" s="13"/>
+      <c r="E38" s="13"/>
+      <c r="F38" s="13"/>
+      <c r="G38" s="13"/>
+      <c r="H38" s="13"/>
+      <c r="I38" s="13"/>
+      <c r="J38" s="13"/>
+      <c r="K38" s="13"/>
+      <c r="L38" s="13"/>
+      <c r="M38" s="13"/>
+    </row>
+    <row r="39" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="11">
+      <c r="B39" s="14">
         <v>10000</v>
       </c>
-      <c r="C39" s="11"/>
-      <c r="D39" s="11">
+      <c r="C39" s="14"/>
+      <c r="D39" s="14">
         <v>30000</v>
       </c>
-      <c r="E39" s="11"/>
-      <c r="F39" s="11">
+      <c r="E39" s="14"/>
+      <c r="F39" s="14">
         <v>50000</v>
       </c>
-      <c r="G39" s="11"/>
-      <c r="H39" s="11">
+      <c r="G39" s="14"/>
+      <c r="H39" s="14">
         <v>100000</v>
       </c>
-      <c r="I39" s="11"/>
-      <c r="J39" s="11">
+      <c r="I39" s="14"/>
+      <c r="J39" s="14">
         <v>300000</v>
       </c>
-      <c r="K39" s="11"/>
-      <c r="L39" s="11">
+      <c r="K39" s="14"/>
+      <c r="L39" s="14">
         <v>500000</v>
       </c>
-      <c r="M39" s="11"/>
-    </row>
-    <row r="40" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="M39" s="14"/>
+    </row>
+    <row r="40" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>45</v>
       </c>
@@ -4349,7 +4379,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>40</v>
       </c>
@@ -4390,7 +4420,7 @@
         <v>1000001</v>
       </c>
     </row>
-    <row r="42" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>42</v>
       </c>
@@ -4431,7 +4461,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="43" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>41</v>
       </c>
@@ -4472,7 +4502,7 @@
         <v>4175014</v>
       </c>
     </row>
-    <row r="44" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>39</v>
       </c>
@@ -4513,7 +4543,7 @@
         <v>28268367</v>
       </c>
     </row>
-    <row r="45" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>38</v>
       </c>
@@ -4554,7 +4584,7 @@
         <v>1499998</v>
       </c>
     </row>
-    <row r="46" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>37</v>
       </c>
@@ -4595,7 +4625,7 @@
         <v>26734635</v>
       </c>
     </row>
-    <row r="47" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>36</v>
       </c>
@@ -4636,7 +4666,7 @@
         <v>18708747</v>
       </c>
     </row>
-    <row r="48" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>35</v>
       </c>
@@ -4801,50 +4831,50 @@
       </c>
     </row>
     <row r="55" spans="1:13" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="10" t="s">
+      <c r="A55" s="13" t="s">
         <v>50</v>
       </c>
-      <c r="B55" s="10"/>
-      <c r="C55" s="10"/>
-      <c r="D55" s="10"/>
-      <c r="E55" s="10"/>
-      <c r="F55" s="10"/>
-      <c r="G55" s="10"/>
-      <c r="H55" s="10"/>
-      <c r="I55" s="10"/>
-      <c r="J55" s="10"/>
-      <c r="K55" s="10"/>
-      <c r="L55" s="10"/>
-      <c r="M55" s="10"/>
+      <c r="B55" s="13"/>
+      <c r="C55" s="13"/>
+      <c r="D55" s="13"/>
+      <c r="E55" s="13"/>
+      <c r="F55" s="13"/>
+      <c r="G55" s="13"/>
+      <c r="H55" s="13"/>
+      <c r="I55" s="13"/>
+      <c r="J55" s="13"/>
+      <c r="K55" s="13"/>
+      <c r="L55" s="13"/>
+      <c r="M55" s="13"/>
     </row>
     <row r="56" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B56" s="11">
+      <c r="B56" s="14">
         <v>10000</v>
       </c>
-      <c r="C56" s="11"/>
-      <c r="D56" s="11">
+      <c r="C56" s="14"/>
+      <c r="D56" s="14">
         <v>30000</v>
       </c>
-      <c r="E56" s="11"/>
-      <c r="F56" s="11">
+      <c r="E56" s="14"/>
+      <c r="F56" s="14">
         <v>50000</v>
       </c>
-      <c r="G56" s="11"/>
-      <c r="H56" s="11">
+      <c r="G56" s="14"/>
+      <c r="H56" s="14">
         <v>100000</v>
       </c>
-      <c r="I56" s="11"/>
-      <c r="J56" s="11">
+      <c r="I56" s="14"/>
+      <c r="J56" s="14">
         <v>300000</v>
       </c>
-      <c r="K56" s="11"/>
-      <c r="L56" s="11">
+      <c r="K56" s="14"/>
+      <c r="L56" s="14">
         <v>500000</v>
       </c>
-      <c r="M56" s="11"/>
+      <c r="M56" s="14"/>
     </row>
     <row r="57" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
@@ -5340,6 +5370,20 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A55:M55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="L56:M56"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A21:M21"/>
     <mergeCell ref="B22:C22"/>
@@ -5354,20 +5398,6 @@
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="L5:M5"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
-    <mergeCell ref="A55:M55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="L56:M56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Report/Measuring.xlsx
+++ b/Report/Measuring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studenthcmusedu-my.sharepoint.com/personal/22127275_student_hcmus_edu_vn/Documents/Programming/DSA/Lab3_Sorting/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="1403" documentId="8_{DA9940A0-0571-4566-AD57-949AA40DBC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F882A60F-7BB8-4345-A79A-BE041592BD31}"/>
+  <xr:revisionPtr revIDLastSave="1406" documentId="8_{DA9940A0-0571-4566-AD57-949AA40DBC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{96EF8C1D-22A0-459E-91B6-CA71CDB4DFCC}"/>
   <bookViews>
-    <workbookView xWindow="8925" yWindow="585" windowWidth="21600" windowHeight="11835" activeTab="1" xr2:uid="{00802968-0738-4320-9C05-4460BE5590E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00802968-0738-4320-9C05-4460BE5590E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Huy" sheetId="1" r:id="rId1"/>
@@ -196,7 +196,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -258,15 +258,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <sz val="14"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="9">
+  <fills count="7">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -301,18 +294,6 @@
       <patternFill patternType="solid">
         <fgColor theme="9"/>
         <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFDDEBF7"/>
-        <bgColor rgb="FF000000"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFF2CC"/>
-        <bgColor rgb="FF000000"/>
       </patternFill>
     </fill>
   </fills>
@@ -365,7 +346,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="3" fontId="2" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
@@ -387,15 +368,6 @@
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="3" fontId="8" fillId="8" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="11" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
@@ -735,74 +707,74 @@
   </cols>
   <sheetData>
     <row r="4" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B4" s="12" t="s">
+      <c r="B4" s="9" t="s">
         <v>40</v>
       </c>
-      <c r="C4" s="12"/>
-      <c r="D4" s="12" t="s">
+      <c r="C4" s="9"/>
+      <c r="D4" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="E4" s="12"/>
-      <c r="F4" s="12" t="s">
+      <c r="E4" s="9"/>
+      <c r="F4" s="9" t="s">
         <v>41</v>
       </c>
-      <c r="G4" s="12"/>
-      <c r="H4" s="12" t="s">
+      <c r="G4" s="9"/>
+      <c r="H4" s="9" t="s">
         <v>39</v>
       </c>
-      <c r="I4" s="12"/>
-      <c r="J4" s="12" t="s">
+      <c r="I4" s="9"/>
+      <c r="J4" s="9" t="s">
         <v>38</v>
       </c>
-      <c r="K4" s="12"/>
-      <c r="L4" s="12" t="s">
+      <c r="K4" s="9"/>
+      <c r="L4" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="M4" s="12"/>
-      <c r="N4" s="12" t="s">
+      <c r="M4" s="9"/>
+      <c r="N4" s="9" t="s">
         <v>36</v>
       </c>
-      <c r="O4" s="12"/>
-      <c r="P4" s="12" t="s">
+      <c r="O4" s="9"/>
+      <c r="P4" s="9" t="s">
         <v>35</v>
       </c>
-      <c r="Q4" s="12"/>
-      <c r="R4" s="12" t="s">
+      <c r="Q4" s="9"/>
+      <c r="R4" s="9" t="s">
         <v>34</v>
       </c>
-      <c r="S4" s="12"/>
-      <c r="T4" s="12" t="s">
+      <c r="S4" s="9"/>
+      <c r="T4" s="9" t="s">
         <v>32</v>
       </c>
-      <c r="U4" s="12"/>
-      <c r="V4" s="12" t="s">
+      <c r="U4" s="9"/>
+      <c r="V4" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="W4" s="12"/>
+      <c r="W4" s="9"/>
     </row>
     <row r="5" spans="1:23" x14ac:dyDescent="0.25">
-      <c r="B5" s="12"/>
-      <c r="C5" s="12"/>
-      <c r="D5" s="12"/>
-      <c r="E5" s="12"/>
-      <c r="F5" s="12"/>
-      <c r="G5" s="12"/>
-      <c r="H5" s="12"/>
-      <c r="I5" s="12"/>
-      <c r="J5" s="12"/>
-      <c r="K5" s="12"/>
-      <c r="L5" s="12"/>
-      <c r="M5" s="12"/>
-      <c r="N5" s="12"/>
-      <c r="O5" s="12"/>
-      <c r="P5" s="12"/>
-      <c r="Q5" s="12"/>
-      <c r="R5" s="12"/>
-      <c r="S5" s="12"/>
-      <c r="T5" s="12"/>
-      <c r="U5" s="12"/>
-      <c r="V5" s="12"/>
-      <c r="W5" s="12"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="9"/>
+      <c r="E5" s="9"/>
+      <c r="F5" s="9"/>
+      <c r="G5" s="9"/>
+      <c r="H5" s="9"/>
+      <c r="I5" s="9"/>
+      <c r="J5" s="9"/>
+      <c r="K5" s="9"/>
+      <c r="L5" s="9"/>
+      <c r="M5" s="9"/>
+      <c r="N5" s="9"/>
+      <c r="O5" s="9"/>
+      <c r="P5" s="9"/>
+      <c r="Q5" s="9"/>
+      <c r="R5" s="9"/>
+      <c r="S5" s="9"/>
+      <c r="T5" s="9"/>
+      <c r="U5" s="9"/>
+      <c r="V5" s="9"/>
+      <c r="W5" s="9"/>
     </row>
     <row r="7" spans="1:23" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
@@ -3032,17 +3004,17 @@
     </row>
   </sheetData>
   <mergeCells count="11">
+    <mergeCell ref="N4:O5"/>
+    <mergeCell ref="P4:Q5"/>
+    <mergeCell ref="R4:S5"/>
+    <mergeCell ref="T4:U5"/>
+    <mergeCell ref="V4:W5"/>
     <mergeCell ref="L4:M5"/>
     <mergeCell ref="B4:C5"/>
     <mergeCell ref="D4:E5"/>
     <mergeCell ref="F4:G5"/>
     <mergeCell ref="H4:I5"/>
     <mergeCell ref="J4:K5"/>
-    <mergeCell ref="N4:O5"/>
-    <mergeCell ref="P4:Q5"/>
-    <mergeCell ref="R4:S5"/>
-    <mergeCell ref="T4:U5"/>
-    <mergeCell ref="V4:W5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
@@ -3054,7 +3026,7 @@
   <sheetPr>
     <tabColor theme="4" tint="0.39997558519241921"/>
   </sheetPr>
-  <dimension ref="A4:R68"/>
+  <dimension ref="A4:M68"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="21.140625" customWidth="1"/>
@@ -3064,53 +3036,53 @@
     <col min="18" max="18" width="23.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="4" spans="1:18" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="13" t="s">
+    <row r="4" spans="1:13" ht="36.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="10" t="s">
         <v>46</v>
       </c>
-      <c r="B4" s="13"/>
-      <c r="C4" s="13"/>
-      <c r="D4" s="13"/>
-      <c r="E4" s="13"/>
-      <c r="F4" s="13"/>
-      <c r="G4" s="13"/>
-      <c r="H4" s="13"/>
-      <c r="I4" s="13"/>
-      <c r="J4" s="13"/>
-      <c r="K4" s="13"/>
-      <c r="L4" s="13"/>
-      <c r="M4" s="13"/>
-    </row>
-    <row r="5" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B4" s="10"/>
+      <c r="C4" s="10"/>
+      <c r="D4" s="10"/>
+      <c r="E4" s="10"/>
+      <c r="F4" s="10"/>
+      <c r="G4" s="10"/>
+      <c r="H4" s="10"/>
+      <c r="I4" s="10"/>
+      <c r="J4" s="10"/>
+      <c r="K4" s="10"/>
+      <c r="L4" s="10"/>
+      <c r="M4" s="10"/>
+    </row>
+    <row r="5" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A5" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B5" s="14">
+      <c r="B5" s="11">
         <v>10000</v>
       </c>
-      <c r="C5" s="14"/>
-      <c r="D5" s="14">
+      <c r="C5" s="11"/>
+      <c r="D5" s="11">
         <v>30000</v>
       </c>
-      <c r="E5" s="14"/>
-      <c r="F5" s="14">
+      <c r="E5" s="11"/>
+      <c r="F5" s="11">
         <v>50000</v>
       </c>
-      <c r="G5" s="14"/>
-      <c r="H5" s="14">
+      <c r="G5" s="11"/>
+      <c r="H5" s="11">
         <v>100000</v>
       </c>
-      <c r="I5" s="14"/>
-      <c r="J5" s="14">
+      <c r="I5" s="11"/>
+      <c r="J5" s="11">
         <v>300000</v>
       </c>
-      <c r="K5" s="14"/>
-      <c r="L5" s="14">
+      <c r="K5" s="11"/>
+      <c r="L5" s="11">
         <v>500000</v>
       </c>
-      <c r="M5" s="14"/>
-    </row>
-    <row r="6" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="M5" s="11"/>
+    </row>
+    <row r="6" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>45</v>
       </c>
@@ -3151,7 +3123,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="7" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A7" s="7" t="s">
         <v>40</v>
       </c>
@@ -3179,24 +3151,20 @@
       <c r="I7" s="2">
         <v>10000066045</v>
       </c>
-      <c r="J7" s="9"/>
-      <c r="K7" s="10"/>
-      <c r="L7" s="11"/>
-      <c r="M7" s="2"/>
-      <c r="O7" s="8">
+      <c r="J7" s="8">
         <v>513952</v>
       </c>
-      <c r="P7" s="2">
+      <c r="K7" s="2">
         <v>90000391152</v>
       </c>
-      <c r="Q7" s="8">
+      <c r="L7" s="8">
         <v>1436930</v>
       </c>
-      <c r="R7" s="2">
+      <c r="M7" s="2">
         <v>249999489560</v>
       </c>
     </row>
-    <row r="8" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A8" s="7" t="s">
         <v>42</v>
       </c>
@@ -3224,32 +3192,20 @@
       <c r="I8" s="2">
         <v>332768</v>
       </c>
-      <c r="J8" s="9">
-        <v>16.330200000000001</v>
-      </c>
-      <c r="K8" s="10">
+      <c r="J8" s="8">
+        <v>10.702400000000001</v>
+      </c>
+      <c r="K8" s="2">
         <v>932768</v>
       </c>
       <c r="L8" s="8">
-        <v>27.058800000000002</v>
+        <v>9.0576000000000008</v>
       </c>
       <c r="M8" s="2">
         <v>1532768</v>
       </c>
-      <c r="O8" s="8">
-        <v>10.702400000000001</v>
-      </c>
-      <c r="P8" s="2">
-        <v>932768</v>
-      </c>
-      <c r="Q8" s="8">
-        <v>9.0576000000000008</v>
-      </c>
-      <c r="R8" s="2">
-        <v>1532768</v>
-      </c>
-    </row>
-    <row r="9" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A9" s="7" t="s">
         <v>41</v>
       </c>
@@ -3277,32 +3233,20 @@
       <c r="I9" s="2">
         <v>1077495</v>
       </c>
-      <c r="J9" s="9">
-        <v>29.6447</v>
-      </c>
-      <c r="K9" s="10">
-        <v>3572703</v>
+      <c r="J9" s="8">
+        <v>26.746200000000002</v>
+      </c>
+      <c r="K9" s="2">
+        <v>3562347</v>
       </c>
       <c r="L9" s="8">
-        <v>46.386699999999998</v>
+        <v>49.616</v>
       </c>
       <c r="M9" s="2">
-        <v>5759747</v>
-      </c>
-      <c r="O9" s="8">
-        <v>26.746200000000002</v>
-      </c>
-      <c r="P9" s="2">
-        <v>3562347</v>
-      </c>
-      <c r="Q9" s="8">
-        <v>49.616</v>
-      </c>
-      <c r="R9" s="2">
         <v>6073735</v>
       </c>
     </row>
-    <row r="10" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A10" s="7" t="s">
         <v>39</v>
       </c>
@@ -3330,32 +3274,20 @@
       <c r="I10" s="2">
         <v>4829292</v>
       </c>
-      <c r="J10" s="9">
-        <v>249.9</v>
-      </c>
-      <c r="K10" s="10">
-        <v>15902205</v>
+      <c r="J10" s="8">
+        <v>119.447</v>
+      </c>
+      <c r="K10" s="2">
+        <v>15902916</v>
       </c>
       <c r="L10" s="8">
-        <v>399.78399999999999</v>
+        <v>196.636</v>
       </c>
       <c r="M10" s="2">
-        <v>27595962</v>
-      </c>
-      <c r="O10" s="8">
-        <v>119.447</v>
-      </c>
-      <c r="P10" s="2">
-        <v>15902916</v>
-      </c>
-      <c r="Q10" s="8">
-        <v>196.636</v>
-      </c>
-      <c r="R10" s="2">
         <v>27594312</v>
       </c>
     </row>
-    <row r="11" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A11" s="7" t="s">
         <v>38</v>
       </c>
@@ -3383,24 +3315,20 @@
       <c r="I11" s="2">
         <v>4996899593</v>
       </c>
-      <c r="J11" s="9"/>
-      <c r="K11" s="10"/>
-      <c r="L11" s="8"/>
-      <c r="M11" s="2"/>
-      <c r="O11" s="8">
+      <c r="J11" s="8">
         <v>137411</v>
       </c>
-      <c r="P11" s="2">
+      <c r="K11" s="2">
         <v>44960162813</v>
       </c>
-      <c r="Q11" s="8">
+      <c r="L11" s="8">
         <v>359524</v>
       </c>
-      <c r="R11" s="2">
+      <c r="M11" s="2">
         <v>125068299550</v>
       </c>
     </row>
-    <row r="12" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A12" s="7" t="s">
         <v>37</v>
       </c>
@@ -3428,32 +3356,20 @@
       <c r="I12" s="2">
         <v>6233721</v>
       </c>
-      <c r="J12" s="9">
-        <v>156.96199999999999</v>
-      </c>
-      <c r="K12" s="10">
-        <v>20346836</v>
+      <c r="J12" s="8">
+        <v>102.27500000000001</v>
+      </c>
+      <c r="K12" s="2">
+        <v>20346547</v>
       </c>
       <c r="L12" s="8">
-        <v>303.06900000000002</v>
+        <v>190.119</v>
       </c>
       <c r="M12" s="2">
-        <v>35177908</v>
-      </c>
-      <c r="O12" s="8">
-        <v>102.27500000000001</v>
-      </c>
-      <c r="P12" s="2">
-        <v>20346547</v>
-      </c>
-      <c r="Q12" s="8">
-        <v>190.119</v>
-      </c>
-      <c r="R12" s="2">
         <v>35178039</v>
       </c>
     </row>
-    <row r="13" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A13" s="7" t="s">
         <v>36</v>
       </c>
@@ -3481,32 +3397,20 @@
       <c r="I13" s="2">
         <v>3863131</v>
       </c>
-      <c r="J13" s="9">
-        <v>106.68899999999999</v>
-      </c>
-      <c r="K13" s="10">
-        <v>14420831</v>
+      <c r="J13" s="8">
+        <v>72.512200000000007</v>
+      </c>
+      <c r="K13" s="2">
+        <v>13711223</v>
       </c>
       <c r="L13" s="8">
-        <v>210.13800000000001</v>
+        <v>114.542</v>
       </c>
       <c r="M13" s="2">
-        <v>27736587</v>
-      </c>
-      <c r="O13" s="8">
-        <v>72.512200000000007</v>
-      </c>
-      <c r="P13" s="2">
-        <v>13711223</v>
-      </c>
-      <c r="Q13" s="8">
-        <v>114.542</v>
-      </c>
-      <c r="R13" s="2">
         <v>25623393</v>
       </c>
     </row>
-    <row r="14" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A14" s="7" t="s">
         <v>35</v>
       </c>
@@ -3534,32 +3438,20 @@
       <c r="I14" s="2">
         <v>1300120</v>
       </c>
-      <c r="J14" s="9">
-        <v>222.79400000000001</v>
-      </c>
-      <c r="K14" s="10">
+      <c r="J14" s="8">
+        <v>86.862899999999996</v>
+      </c>
+      <c r="K14" s="2">
         <v>3900120</v>
       </c>
       <c r="L14" s="8">
-        <v>362.94099999999997</v>
+        <v>139.51599999999999</v>
       </c>
       <c r="M14" s="2">
         <v>6500120</v>
       </c>
-      <c r="O14" s="8">
-        <v>86.862899999999996</v>
-      </c>
-      <c r="P14" s="2">
-        <v>3900120</v>
-      </c>
-      <c r="Q14" s="8">
-        <v>139.51599999999999</v>
-      </c>
-      <c r="R14" s="2">
-        <v>6500120</v>
-      </c>
-    </row>
-    <row r="15" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A15" s="7" t="s">
         <v>34</v>
       </c>
@@ -3587,24 +3479,20 @@
       <c r="I15" s="2">
         <v>10000199998</v>
       </c>
-      <c r="J15" s="9"/>
-      <c r="K15" s="10"/>
-      <c r="L15" s="8"/>
-      <c r="M15" s="2"/>
-      <c r="O15" s="8">
+      <c r="J15" s="8">
         <v>215658</v>
       </c>
-      <c r="P15" s="2">
+      <c r="K15" s="2">
         <v>90000599998</v>
       </c>
-      <c r="Q15" s="8">
+      <c r="L15" s="8">
         <v>598300</v>
       </c>
-      <c r="R15" s="2">
+      <c r="M15" s="2">
         <v>250000999998</v>
       </c>
     </row>
-    <row r="16" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A16" s="7" t="s">
         <v>32</v>
       </c>
@@ -3632,24 +3520,20 @@
       <c r="I16" s="2">
         <v>7484826744</v>
       </c>
-      <c r="J16" s="8"/>
-      <c r="K16" s="2"/>
-      <c r="L16" s="8"/>
-      <c r="M16" s="2"/>
-      <c r="O16" s="8">
+      <c r="J16" s="8">
         <v>382225</v>
       </c>
-      <c r="P16" s="2">
+      <c r="K16" s="2">
         <v>67311957498</v>
       </c>
-      <c r="Q16" s="8">
+      <c r="L16" s="8">
         <v>1038750</v>
       </c>
-      <c r="R16" s="2">
+      <c r="M16" s="2">
         <v>187697095158</v>
       </c>
     </row>
-    <row r="17" spans="1:18" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:13" ht="23.25" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A17" s="7" t="s">
         <v>33</v>
       </c>
@@ -3678,77 +3562,65 @@
         <v>8383847</v>
       </c>
       <c r="J17" s="8">
-        <v>45.911999999999999</v>
+        <v>120.20099999999999</v>
       </c>
       <c r="K17" s="2">
-        <v>31948207</v>
+        <v>30918022</v>
       </c>
       <c r="L17" s="8">
-        <v>113.16800000000001</v>
+        <v>222.84299999999999</v>
       </c>
       <c r="M17" s="2">
-        <v>59722045</v>
-      </c>
-      <c r="O17" s="8">
-        <v>120.20099999999999</v>
-      </c>
-      <c r="P17" s="2">
-        <v>30918022</v>
-      </c>
-      <c r="Q17" s="8">
-        <v>222.84299999999999</v>
-      </c>
-      <c r="R17" s="2">
         <v>59976940</v>
       </c>
     </row>
-    <row r="21" spans="1:18" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A21" s="13" t="s">
+    <row r="21" spans="1:13" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A21" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="B21" s="13"/>
-      <c r="C21" s="13"/>
-      <c r="D21" s="13"/>
-      <c r="E21" s="13"/>
-      <c r="F21" s="13"/>
-      <c r="G21" s="13"/>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13"/>
-      <c r="J21" s="13"/>
-      <c r="K21" s="13"/>
-      <c r="L21" s="13"/>
-      <c r="M21" s="13"/>
-    </row>
-    <row r="22" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B21" s="10"/>
+      <c r="C21" s="10"/>
+      <c r="D21" s="10"/>
+      <c r="E21" s="10"/>
+      <c r="F21" s="10"/>
+      <c r="G21" s="10"/>
+      <c r="H21" s="10"/>
+      <c r="I21" s="10"/>
+      <c r="J21" s="10"/>
+      <c r="K21" s="10"/>
+      <c r="L21" s="10"/>
+      <c r="M21" s="10"/>
+    </row>
+    <row r="22" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A22" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B22" s="14">
+      <c r="B22" s="11">
         <v>10000</v>
       </c>
-      <c r="C22" s="14"/>
-      <c r="D22" s="14">
+      <c r="C22" s="11"/>
+      <c r="D22" s="11">
         <v>30000</v>
       </c>
-      <c r="E22" s="14"/>
-      <c r="F22" s="14">
+      <c r="E22" s="11"/>
+      <c r="F22" s="11">
         <v>50000</v>
       </c>
-      <c r="G22" s="14"/>
-      <c r="H22" s="14">
+      <c r="G22" s="11"/>
+      <c r="H22" s="11">
         <v>100000</v>
       </c>
-      <c r="I22" s="14"/>
-      <c r="J22" s="14">
+      <c r="I22" s="11"/>
+      <c r="J22" s="11">
         <v>300000</v>
       </c>
-      <c r="K22" s="14"/>
-      <c r="L22" s="14">
+      <c r="K22" s="11"/>
+      <c r="L22" s="11">
         <v>500000</v>
       </c>
-      <c r="M22" s="14"/>
-    </row>
-    <row r="23" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="M22" s="11"/>
+    </row>
+    <row r="23" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A23" s="4" t="s">
         <v>45</v>
       </c>
@@ -3789,7 +3661,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="24" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A24" s="7" t="s">
         <v>40</v>
       </c>
@@ -3817,24 +3689,20 @@
       <c r="I24" s="2">
         <v>3713613057</v>
       </c>
-      <c r="J24" s="8"/>
-      <c r="K24" s="2"/>
-      <c r="L24" s="8"/>
-      <c r="M24" s="2"/>
-      <c r="O24" s="8">
+      <c r="J24" s="8">
         <v>40094</v>
       </c>
-      <c r="P24" s="2">
+      <c r="K24" s="2">
         <v>16565019901</v>
       </c>
-      <c r="Q24" s="8">
+      <c r="L24" s="8">
         <v>27860.6</v>
       </c>
-      <c r="R24" s="2">
+      <c r="M24" s="2">
         <v>11842359776</v>
       </c>
     </row>
-    <row r="25" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A25" s="7" t="s">
         <v>42</v>
       </c>
@@ -3863,27 +3731,19 @@
         <v>400000</v>
       </c>
       <c r="J25" s="8">
-        <v>25.383600000000001</v>
+        <v>10.995699999999999</v>
       </c>
       <c r="K25" s="2">
         <v>1200000</v>
       </c>
-      <c r="L25" s="8"/>
-      <c r="M25" s="2"/>
-      <c r="O25" s="8">
-        <v>10.995699999999999</v>
-      </c>
-      <c r="P25" s="2">
-        <v>1200000</v>
-      </c>
-      <c r="Q25" s="8">
+      <c r="L25" s="8">
         <v>15.128299999999999</v>
       </c>
-      <c r="R25" s="2">
+      <c r="M25" s="2">
         <v>2000000</v>
       </c>
     </row>
-    <row r="26" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A26" s="7" t="s">
         <v>41</v>
       </c>
@@ -3912,27 +3772,19 @@
         <v>835023</v>
       </c>
       <c r="J26" s="8">
-        <v>26.213999999999999</v>
+        <v>10.401199999999999</v>
       </c>
       <c r="K26" s="2">
-        <v>2505033</v>
-      </c>
-      <c r="L26" s="8"/>
-      <c r="M26" s="2"/>
-      <c r="O26" s="8">
-        <v>10.401199999999999</v>
-      </c>
-      <c r="P26" s="2">
         <v>2505034</v>
       </c>
-      <c r="Q26" s="8">
+      <c r="L26" s="8">
         <v>16.7559</v>
       </c>
-      <c r="R26" s="2">
+      <c r="M26" s="2">
         <v>4175025</v>
       </c>
     </row>
-    <row r="27" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A27" s="7" t="s">
         <v>39</v>
       </c>
@@ -3960,24 +3812,20 @@
       <c r="I27" s="2">
         <v>4969320</v>
       </c>
-      <c r="J27" s="8"/>
-      <c r="K27" s="2"/>
-      <c r="L27" s="8"/>
-      <c r="M27" s="2"/>
-      <c r="O27" s="8">
+      <c r="J27" s="8">
         <v>102.003</v>
       </c>
-      <c r="P27" s="2">
+      <c r="K27" s="2">
         <v>16322175</v>
       </c>
-      <c r="Q27" s="8">
+      <c r="L27" s="8">
         <v>170.22499999999999</v>
       </c>
-      <c r="R27" s="2">
+      <c r="M27" s="2">
         <v>28268334</v>
       </c>
     </row>
-    <row r="28" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A28" s="7" t="s">
         <v>38</v>
       </c>
@@ -4005,24 +3853,20 @@
       <c r="I28" s="2">
         <v>743862</v>
       </c>
-      <c r="J28" s="8"/>
-      <c r="K28" s="2"/>
-      <c r="L28" s="8"/>
-      <c r="M28" s="2"/>
-      <c r="O28" s="8">
+      <c r="J28" s="8">
         <v>4.3433000000000002</v>
       </c>
-      <c r="P28" s="2">
+      <c r="K28" s="2">
         <v>1362474</v>
       </c>
-      <c r="Q28" s="8">
+      <c r="L28" s="8">
         <v>4.9542000000000002</v>
       </c>
-      <c r="R28" s="2">
+      <c r="M28" s="2">
         <v>1690026</v>
       </c>
     </row>
-    <row r="29" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A29" s="7" t="s">
         <v>37</v>
       </c>
@@ -4050,24 +3894,20 @@
       <c r="I29" s="2">
         <v>4900830</v>
       </c>
-      <c r="J29" s="8"/>
-      <c r="K29" s="2"/>
-      <c r="L29" s="8"/>
-      <c r="M29" s="2"/>
-      <c r="O29" s="8">
+      <c r="J29" s="8">
         <v>67.150499999999994</v>
       </c>
-      <c r="P29" s="2">
+      <c r="K29" s="2">
         <v>15650920</v>
       </c>
-      <c r="Q29" s="8">
+      <c r="L29" s="8">
         <v>121.15</v>
       </c>
-      <c r="R29" s="2">
+      <c r="M29" s="2">
         <v>26806893</v>
       </c>
     </row>
-    <row r="30" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A30" s="7" t="s">
         <v>36</v>
       </c>
@@ -4095,24 +3935,20 @@
       <c r="I30" s="2">
         <v>3579619</v>
       </c>
-      <c r="J30" s="8"/>
-      <c r="K30" s="2"/>
-      <c r="L30" s="8"/>
-      <c r="M30" s="2"/>
-      <c r="O30" s="8">
+      <c r="J30" s="8">
         <v>42.811399999999999</v>
       </c>
-      <c r="P30" s="2">
+      <c r="K30" s="2">
         <v>11069303</v>
       </c>
-      <c r="Q30" s="8">
+      <c r="L30" s="8">
         <v>77.176599999999993</v>
       </c>
-      <c r="R30" s="2">
+      <c r="M30" s="2">
         <v>18905233</v>
       </c>
     </row>
-    <row r="31" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A31" s="7" t="s">
         <v>35</v>
       </c>
@@ -4140,24 +3976,20 @@
       <c r="I31" s="2">
         <v>1300120</v>
       </c>
-      <c r="J31" s="8"/>
-      <c r="K31" s="2"/>
-      <c r="L31" s="8"/>
-      <c r="M31" s="2"/>
-      <c r="O31" s="8">
+      <c r="J31" s="8">
         <v>83.856399999999994</v>
       </c>
-      <c r="P31" s="2">
+      <c r="K31" s="2">
         <v>4500143</v>
       </c>
-      <c r="Q31" s="8">
+      <c r="L31" s="8">
         <v>144.67400000000001</v>
       </c>
-      <c r="R31" s="2">
+      <c r="M31" s="2">
         <v>7500143</v>
       </c>
     </row>
-    <row r="32" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A32" s="7" t="s">
         <v>34</v>
       </c>
@@ -4185,24 +4017,20 @@
       <c r="I32" s="2">
         <v>10000199998</v>
       </c>
-      <c r="J32" s="8"/>
-      <c r="K32" s="2"/>
-      <c r="L32" s="8"/>
-      <c r="M32" s="2"/>
-      <c r="O32" s="8">
+      <c r="J32" s="8">
         <v>214278</v>
       </c>
-      <c r="P32" s="2">
+      <c r="K32" s="2">
         <v>90000599998</v>
       </c>
-      <c r="Q32" s="8">
+      <c r="L32" s="8">
         <v>582223</v>
       </c>
-      <c r="R32" s="2">
+      <c r="M32" s="2">
         <v>250000999998</v>
       </c>
     </row>
-    <row r="33" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A33" s="7" t="s">
         <v>32</v>
       </c>
@@ -4230,24 +4058,20 @@
       <c r="I33" s="2">
         <v>2799818</v>
       </c>
-      <c r="J33" s="8"/>
-      <c r="K33" s="2"/>
-      <c r="L33" s="8"/>
-      <c r="M33" s="2"/>
-      <c r="O33" s="8">
+      <c r="J33" s="8">
         <v>30.553000000000001</v>
       </c>
-      <c r="P33" s="2">
+      <c r="K33" s="2">
         <v>11999620</v>
       </c>
-      <c r="Q33" s="8">
+      <c r="L33" s="8">
         <v>51.583199999999998</v>
       </c>
-      <c r="R33" s="2">
+      <c r="M33" s="2">
         <v>17999694</v>
       </c>
     </row>
-    <row r="34" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A34" s="7" t="s">
         <v>33</v>
       </c>
@@ -4275,70 +4099,66 @@
       <c r="I34" s="2">
         <v>3062589</v>
       </c>
-      <c r="J34" s="8"/>
-      <c r="K34" s="2"/>
-      <c r="L34" s="8"/>
-      <c r="M34" s="2"/>
-      <c r="O34" s="8">
+      <c r="J34" s="8">
         <v>26.707100000000001</v>
       </c>
-      <c r="P34" s="2">
+      <c r="K34" s="2">
         <v>9816956</v>
       </c>
-      <c r="Q34" s="8">
+      <c r="L34" s="8">
         <v>47.722900000000003</v>
       </c>
-      <c r="R34" s="2">
+      <c r="M34" s="2">
         <v>16954347</v>
       </c>
     </row>
-    <row r="38" spans="1:18" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A38" s="13" t="s">
+    <row r="38" spans="1:13" ht="46.5" x14ac:dyDescent="0.25">
+      <c r="A38" s="10" t="s">
         <v>49</v>
       </c>
-      <c r="B38" s="13"/>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
-      <c r="G38" s="13"/>
-      <c r="H38" s="13"/>
-      <c r="I38" s="13"/>
-      <c r="J38" s="13"/>
-      <c r="K38" s="13"/>
-      <c r="L38" s="13"/>
-      <c r="M38" s="13"/>
-    </row>
-    <row r="39" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="B38" s="10"/>
+      <c r="C38" s="10"/>
+      <c r="D38" s="10"/>
+      <c r="E38" s="10"/>
+      <c r="F38" s="10"/>
+      <c r="G38" s="10"/>
+      <c r="H38" s="10"/>
+      <c r="I38" s="10"/>
+      <c r="J38" s="10"/>
+      <c r="K38" s="10"/>
+      <c r="L38" s="10"/>
+      <c r="M38" s="10"/>
+    </row>
+    <row r="39" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A39" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B39" s="14">
+      <c r="B39" s="11">
         <v>10000</v>
       </c>
-      <c r="C39" s="14"/>
-      <c r="D39" s="14">
+      <c r="C39" s="11"/>
+      <c r="D39" s="11">
         <v>30000</v>
       </c>
-      <c r="E39" s="14"/>
-      <c r="F39" s="14">
+      <c r="E39" s="11"/>
+      <c r="F39" s="11">
         <v>50000</v>
       </c>
-      <c r="G39" s="14"/>
-      <c r="H39" s="14">
+      <c r="G39" s="11"/>
+      <c r="H39" s="11">
         <v>100000</v>
       </c>
-      <c r="I39" s="14"/>
-      <c r="J39" s="14">
+      <c r="I39" s="11"/>
+      <c r="J39" s="11">
         <v>300000</v>
       </c>
-      <c r="K39" s="14"/>
-      <c r="L39" s="14">
+      <c r="K39" s="11"/>
+      <c r="L39" s="11">
         <v>500000</v>
       </c>
-      <c r="M39" s="14"/>
-    </row>
-    <row r="40" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+      <c r="M39" s="11"/>
+    </row>
+    <row r="40" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A40" s="4" t="s">
         <v>45</v>
       </c>
@@ -4379,7 +4199,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="41" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A41" s="7" t="s">
         <v>40</v>
       </c>
@@ -4420,7 +4240,7 @@
         <v>1000001</v>
       </c>
     </row>
-    <row r="42" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A42" s="7" t="s">
         <v>42</v>
       </c>
@@ -4461,7 +4281,7 @@
         <v>2000000</v>
       </c>
     </row>
-    <row r="43" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A43" s="7" t="s">
         <v>41</v>
       </c>
@@ -4502,7 +4322,7 @@
         <v>4175014</v>
       </c>
     </row>
-    <row r="44" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A44" s="7" t="s">
         <v>39</v>
       </c>
@@ -4543,7 +4363,7 @@
         <v>28268367</v>
       </c>
     </row>
-    <row r="45" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A45" s="7" t="s">
         <v>38</v>
       </c>
@@ -4584,7 +4404,7 @@
         <v>1499998</v>
       </c>
     </row>
-    <row r="46" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A46" s="7" t="s">
         <v>37</v>
       </c>
@@ -4625,7 +4445,7 @@
         <v>26734635</v>
       </c>
     </row>
-    <row r="47" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A47" s="7" t="s">
         <v>36</v>
       </c>
@@ -4666,7 +4486,7 @@
         <v>18708747</v>
       </c>
     </row>
-    <row r="48" spans="1:18" ht="18.75" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A48" s="7" t="s">
         <v>35</v>
       </c>
@@ -4831,50 +4651,50 @@
       </c>
     </row>
     <row r="55" spans="1:13" ht="46.5" x14ac:dyDescent="0.25">
-      <c r="A55" s="13" t="s">
+      <c r="A55" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="B55" s="13"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
-      <c r="G55" s="13"/>
-      <c r="H55" s="13"/>
-      <c r="I55" s="13"/>
-      <c r="J55" s="13"/>
-      <c r="K55" s="13"/>
-      <c r="L55" s="13"/>
-      <c r="M55" s="13"/>
+      <c r="B55" s="10"/>
+      <c r="C55" s="10"/>
+      <c r="D55" s="10"/>
+      <c r="E55" s="10"/>
+      <c r="F55" s="10"/>
+      <c r="G55" s="10"/>
+      <c r="H55" s="10"/>
+      <c r="I55" s="10"/>
+      <c r="J55" s="10"/>
+      <c r="K55" s="10"/>
+      <c r="L55" s="10"/>
+      <c r="M55" s="10"/>
     </row>
     <row r="56" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A56" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="B56" s="14">
+      <c r="B56" s="11">
         <v>10000</v>
       </c>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14">
+      <c r="C56" s="11"/>
+      <c r="D56" s="11">
         <v>30000</v>
       </c>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14">
+      <c r="E56" s="11"/>
+      <c r="F56" s="11">
         <v>50000</v>
       </c>
-      <c r="G56" s="14"/>
-      <c r="H56" s="14">
+      <c r="G56" s="11"/>
+      <c r="H56" s="11">
         <v>100000</v>
       </c>
-      <c r="I56" s="14"/>
-      <c r="J56" s="14">
+      <c r="I56" s="11"/>
+      <c r="J56" s="11">
         <v>300000</v>
       </c>
-      <c r="K56" s="14"/>
-      <c r="L56" s="14">
+      <c r="K56" s="11"/>
+      <c r="L56" s="11">
         <v>500000</v>
       </c>
-      <c r="M56" s="14"/>
+      <c r="M56" s="11"/>
     </row>
     <row r="57" spans="1:13" ht="18.75" x14ac:dyDescent="0.3">
       <c r="A57" s="4" t="s">
@@ -5370,20 +5190,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="A55:M55"/>
-    <mergeCell ref="B56:C56"/>
-    <mergeCell ref="D56:E56"/>
-    <mergeCell ref="F56:G56"/>
-    <mergeCell ref="H56:I56"/>
-    <mergeCell ref="J56:K56"/>
-    <mergeCell ref="L56:M56"/>
-    <mergeCell ref="A38:M38"/>
-    <mergeCell ref="B39:C39"/>
-    <mergeCell ref="D39:E39"/>
-    <mergeCell ref="F39:G39"/>
-    <mergeCell ref="H39:I39"/>
-    <mergeCell ref="J39:K39"/>
-    <mergeCell ref="L39:M39"/>
     <mergeCell ref="A4:M4"/>
     <mergeCell ref="A21:M21"/>
     <mergeCell ref="B22:C22"/>
@@ -5398,6 +5204,20 @@
     <mergeCell ref="H5:I5"/>
     <mergeCell ref="J5:K5"/>
     <mergeCell ref="L5:M5"/>
+    <mergeCell ref="A38:M38"/>
+    <mergeCell ref="B39:C39"/>
+    <mergeCell ref="D39:E39"/>
+    <mergeCell ref="F39:G39"/>
+    <mergeCell ref="H39:I39"/>
+    <mergeCell ref="J39:K39"/>
+    <mergeCell ref="L39:M39"/>
+    <mergeCell ref="A55:M55"/>
+    <mergeCell ref="B56:C56"/>
+    <mergeCell ref="D56:E56"/>
+    <mergeCell ref="F56:G56"/>
+    <mergeCell ref="H56:I56"/>
+    <mergeCell ref="J56:K56"/>
+    <mergeCell ref="L56:M56"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>

--- a/Report/Measuring.xlsx
+++ b/Report/Measuring.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studenthcmusedu-my.sharepoint.com/personal/22127275_student_hcmus_edu_vn/Documents/Programming/DSA/Lab3_Sorting/Report/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2290" documentId="8_{DA9940A0-0571-4566-AD57-949AA40DBC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{A8500913-A52A-4F84-915A-74850A9F63EF}"/>
+  <xr:revisionPtr revIDLastSave="2317" documentId="8_{DA9940A0-0571-4566-AD57-949AA40DBC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4698F8FA-A5FA-4619-83BC-E7B2AAD6D1C2}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00802968-0738-4320-9C05-4460BE5590E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00802968-0738-4320-9C05-4460BE5590E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -38,7 +38,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="208" uniqueCount="24">
   <si>
     <t>Shaker Sort</t>
   </si>
@@ -107,6 +107,9 @@
   </si>
   <si>
     <t>Reverse data input</t>
+  </si>
+  <si>
+    <t>Reversed data input</t>
   </si>
 </sst>
 </file>
@@ -1928,11 +1931,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$41</c:f>
+              <c:f>Comparison!$B$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Quick Sort</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -1948,62 +1951,55 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$34:$G$34</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$41:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$41:$G$41</c:f>
+              <c:f>Comparison!$B$41:$B$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>262447</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>880323</c:v>
+                  <c:v>110097</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1548623</c:v>
+                  <c:v>100019998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3297215</c:v>
+                  <c:v>39998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>10805247</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>18708747</c:v>
+                  <c:v>225757</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C4AE-4032-9E8F-52B2376E280C}"/>
+              <c16:uniqueId val="{00000000-0F26-4CF6-BA02-68803CA2EE9F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2012,11 +2008,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$42</c:f>
+              <c:f>Comparison!$C$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Radix Sort</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2032,62 +2028,55 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$34:$G$34</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$41:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$42:$G$42</c:f>
+              <c:f>Comparison!$C$41:$C$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>110097</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>880323</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>390120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>650120</c:v>
+                  <c:v>900059998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1300120</c:v>
+                  <c:v>119998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4500143</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7500143</c:v>
+                  <c:v>767188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C4AE-4032-9E8F-52B2376E280C}"/>
+              <c16:uniqueId val="{00000001-0F26-4CF6-BA02-68803CA2EE9F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2096,11 +2085,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$43</c:f>
+              <c:f>Comparison!$D$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Selection Sort</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2116,62 +2105,55 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$34:$G$34</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$41:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$43:$G$43</c:f>
+              <c:f>Comparison!$D$41:$D$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>100019998</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1548623</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>900059998</c:v>
+                  <c:v>650120</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2500099998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10000199998</c:v>
+                  <c:v>199998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90000599998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>250000999998</c:v>
+                  <c:v>1367188</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C4AE-4032-9E8F-52B2376E280C}"/>
+              <c16:uniqueId val="{00000002-0F26-4CF6-BA02-68803CA2EE9F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2180,11 +2162,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$44</c:f>
+              <c:f>Comparison!$E$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Shaker Sort</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2200,62 +2182,55 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$34:$G$34</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$41:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$44:$G$44</c:f>
+              <c:f>Comparison!$E$41:$E$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>39998</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3297215</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>119998</c:v>
+                  <c:v>1300120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>199998</c:v>
+                  <c:v>10000199998</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>399998</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1199998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>1999998</c:v>
+                  <c:v>2901472</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C4AE-4032-9E8F-52B2376E280C}"/>
+              <c16:uniqueId val="{00000003-0F26-4CF6-BA02-68803CA2EE9F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2264,11 +2239,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$45</c:f>
+              <c:f>Comparison!$F$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Shell Sort</c:v>
+                  <c:v>300000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2284,62 +2259,132 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$34:$G$34</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$41:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$45:$G$45</c:f>
+              <c:f>Comparison!$F$41:$F$45</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>225757</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>10805247</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>767188</c:v>
+                  <c:v>4500143</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1367188</c:v>
+                  <c:v>90000599998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>2901472</c:v>
+                  <c:v>1199998</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>9604315</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>16804315</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-C4AE-4032-9E8F-52B2376E280C}"/>
+              <c16:uniqueId val="{00000005-0F26-4CF6-BA02-68803CA2EE9F}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparison!$G$34</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>500000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$41:$A$45</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Radix Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Shaker Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$G$41:$G$45</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>18708747</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7500143</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>250000999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>1999998</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16804315</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-0F26-4CF6-BA02-68803CA2EE9F}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2750,11 +2795,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$50</c:f>
+              <c:f>Comparison!$B$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Bubble Sort</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2770,35 +2815,34 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$49:$G$49</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$50:$A$55</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$50:$G$50</c:f>
+              <c:f>Comparison!$B$50:$B$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
@@ -2806,26 +2850,26 @@
                   <c:v>100019998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>900059998</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2500099998</c:v>
+                  <c:v>81018</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10000199998</c:v>
+                  <c:v>370080</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>26026918920</c:v>
+                  <c:v>100009999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>250000999998</c:v>
+                  <c:v>456443</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-C20E-45F8-B7AD-7E8FEAB47DE5}"/>
+              <c16:uniqueId val="{00000000-D8D8-4C90-8319-7AB2E215126D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2834,11 +2878,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$51</c:f>
+              <c:f>Comparison!$C$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Counting Sort</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2854,62 +2898,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$49:$G$49</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$50:$A$55</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$51:$G$51</c:f>
+              <c:f>Comparison!$C$50:$C$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>40000</c:v>
+                  <c:v>900059998</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>120000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>200000</c:v>
+                  <c:v>243018</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>400000</c:v>
+                  <c:v>1253673</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1200000</c:v>
+                  <c:v>900029999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000000</c:v>
+                  <c:v>1513467</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-C20E-45F8-B7AD-7E8FEAB47DE5}"/>
+              <c16:uniqueId val="{00000001-D8D8-4C90-8319-7AB2E215126D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -2918,11 +2961,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$52</c:f>
+              <c:f>Comparison!$D$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Flash Sort</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -2938,62 +2981,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$49:$G$49</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$50:$A$55</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$52:$G$52</c:f>
+              <c:f>Comparison!$D$50:$D$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>81018</c:v>
+                  <c:v>2500099998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>243018</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>405018</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>810018</c:v>
+                  <c:v>2199228</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2430018</c:v>
+                  <c:v>2500049999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4050018</c:v>
+                  <c:v>2633947</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-C20E-45F8-B7AD-7E8FEAB47DE5}"/>
+              <c16:uniqueId val="{00000002-D8D8-4C90-8319-7AB2E215126D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3002,11 +3044,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$53</c:f>
+              <c:f>Comparison!$E$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Heap Sort</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3022,62 +3064,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$49:$G$49</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$50:$A$55</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$53:$G$53</c:f>
+              <c:f>Comparison!$E$50:$E$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>370080</c:v>
+                  <c:v>10000199998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1253673</c:v>
+                  <c:v>400000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2199228</c:v>
+                  <c:v>810018</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4690131</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15511497</c:v>
+                  <c:v>10000099999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26967846</c:v>
+                  <c:v>5567899</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-C20E-45F8-B7AD-7E8FEAB47DE5}"/>
+              <c16:uniqueId val="{00000003-D8D8-4C90-8319-7AB2E215126D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3086,11 +3127,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$54</c:f>
+              <c:f>Comparison!$F$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Insertion Sort</c:v>
+                  <c:v>300000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3106,62 +3147,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$49:$G$49</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$50:$A$55</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$54:$G$54</c:f>
+              <c:f>Comparison!$F$50:$F$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>100009999</c:v>
+                  <c:v>26026918920</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>900029999</c:v>
+                  <c:v>1200000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2500049999</c:v>
+                  <c:v>2430018</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10000099999</c:v>
+                  <c:v>15511497</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>90000299999</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>250000499999</c:v>
+                  <c:v>18108315</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-C20E-45F8-B7AD-7E8FEAB47DE5}"/>
+              <c16:uniqueId val="{00000004-D8D8-4C90-8319-7AB2E215126D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3170,11 +3210,11 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$55</c:f>
+              <c:f>Comparison!$G$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Merge Sort</c:v>
+                  <c:v>500000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3190,52 +3230,51 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$49:$G$49</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$50:$A$55</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$55:$G$55</c:f>
+              <c:f>Comparison!$G$50:$G$55</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>456443</c:v>
+                  <c:v>250000999998</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1513467</c:v>
+                  <c:v>2000000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2633947</c:v>
+                  <c:v>4050018</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>5567899</c:v>
+                  <c:v>26967846</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>18108315</c:v>
+                  <c:v>250000499999</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>31336411</c:v>
@@ -3245,7 +3284,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-C20E-45F8-B7AD-7E8FEAB47DE5}"/>
+              <c16:uniqueId val="{00000005-D8D8-4C90-8319-7AB2E215126D}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3654,11 +3693,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$56</c:f>
+              <c:f>Comparison!$B$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Quick Sort</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3673,36 +3712,56 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$56:$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Radix Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Shaker Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$56:$G$56</c:f>
+              <c:f>Comparison!$B$56:$B$60</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
+                <c:ptCount val="5"/>
                 <c:pt idx="0">
                   <c:v>460819</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1622379</c:v>
+                  <c:v>110097</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2885671</c:v>
+                  <c:v>100019998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6270885</c:v>
+                  <c:v>100010001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>21176461</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>37174571</c:v>
+                  <c:v>324408</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-8F8E-4D9F-9D74-2C15BECAE3AC}"/>
+              <c16:uniqueId val="{00000000-B25A-432C-855E-137AB8A03875}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3711,11 +3770,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$57</c:f>
+              <c:f>Comparison!$C$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Radix Sort</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3730,36 +3789,56 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$56:$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Radix Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Shaker Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$57:$G$57</c:f>
+              <c:f>Comparison!$C$56:$C$60</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>110097</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1622379</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>390120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>650120</c:v>
+                  <c:v>900059998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1300120</c:v>
+                  <c:v>900030001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>4500143</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7500143</c:v>
+                  <c:v>1119932</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-8F8E-4D9F-9D74-2C15BECAE3AC}"/>
+              <c16:uniqueId val="{00000001-B25A-432C-855E-137AB8A03875}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3768,11 +3847,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$58</c:f>
+              <c:f>Comparison!$D$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Selection Sort</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3787,36 +3866,56 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$56:$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Radix Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Shaker Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$58:$G$58</c:f>
+              <c:f>Comparison!$D$56:$D$60</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>100019998</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>2885671</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>900059998</c:v>
+                  <c:v>650120</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2500099998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10000199998</c:v>
+                  <c:v>2500050001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90000599998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>250000999998</c:v>
+                  <c:v>1871455</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-8F8E-4D9F-9D74-2C15BECAE3AC}"/>
+              <c16:uniqueId val="{00000002-B25A-432C-855E-137AB8A03875}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3825,11 +3924,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$59</c:f>
+              <c:f>Comparison!$E$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Shaker Sort</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3844,36 +3943,56 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$56:$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Radix Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Shaker Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$59:$G$59</c:f>
+              <c:f>Comparison!$E$56:$E$60</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>100010001</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>6270885</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>900030001</c:v>
+                  <c:v>1300120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2500050001</c:v>
+                  <c:v>10000199998</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>10000100001</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90000300001</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>250000500001</c:v>
+                  <c:v>4087474</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-8F8E-4D9F-9D74-2C15BECAE3AC}"/>
+              <c16:uniqueId val="{00000003-B25A-432C-855E-137AB8A03875}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -3882,11 +4001,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$60</c:f>
+              <c:f>Comparison!$F$49</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Shell Sort</c:v>
+                  <c:v>300000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -3901,36 +4020,133 @@
             <a:effectLst/>
           </c:spPr>
           <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$56:$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Radix Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Shaker Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$60:$G$60</c:f>
+              <c:f>Comparison!$F$56:$F$60</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>324408</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>21176461</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1119932</c:v>
+                  <c:v>4500143</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1871455</c:v>
+                  <c:v>90000599998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4087474</c:v>
+                  <c:v>90000300001</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>13417878</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>23277263</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-8F8E-4D9F-9D74-2C15BECAE3AC}"/>
+              <c16:uniqueId val="{00000004-B25A-432C-855E-137AB8A03875}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparison!$G$49</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>500000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$56:$A$60</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Radix Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Shaker Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$G$56:$G$60</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>37174571</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7500143</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>250000999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>250000500001</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>23277263</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000005-B25A-432C-855E-137AB8A03875}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -4014,6 +4230,7 @@
             </a:p>
           </c:txPr>
         </c:title>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
         <c:majorTickMark val="none"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -8751,11 +8968,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$5</c:f>
+              <c:f>Comparison!$B$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Bubble Sort</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8771,35 +8988,34 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$4:$G$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$5:$A$10</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$5:$G$5</c:f>
+              <c:f>Comparison!$B$5:$B$10</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
@@ -8807,26 +9023,26 @@
                   <c:v>99942160</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>900050001</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2500032920</c:v>
+                  <c:v>103308</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10000066045</c:v>
+                  <c:v>383118</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90000391152</c:v>
+                  <c:v>50126147</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>249999489560</c:v>
+                  <c:v>506975</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-1F21-483E-9B53-5576CF558DA3}"/>
+              <c16:uniqueId val="{00000001-8994-4B5A-A9DB-B8492F1E0B06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8835,11 +9051,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$6</c:f>
+              <c:f>Comparison!$C$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Counting Sort</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8855,62 +9071,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$4:$G$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$5:$A$10</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$6:$G$6</c:f>
+              <c:f>Comparison!$C$5:$C$10</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>40000</c:v>
+                  <c:v>900050001</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>120000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>182768</c:v>
+                  <c:v>330477</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>332768</c:v>
+                  <c:v>1290735</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>932768</c:v>
+                  <c:v>451707034</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1532768</c:v>
+                  <c:v>1684990</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-1F21-483E-9B53-5576CF558DA3}"/>
+              <c16:uniqueId val="{00000002-8994-4B5A-A9DB-B8492F1E0B06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -8919,11 +9134,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$7</c:f>
+              <c:f>Comparison!$D$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Flash Sort</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -8939,62 +9154,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$4:$G$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$5:$A$10</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$7:$G$7</c:f>
+              <c:f>Comparison!$D$5:$D$10</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>103308</c:v>
+                  <c:v>2500032920</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>330477</c:v>
+                  <c:v>182768</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>544705</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1047503</c:v>
+                  <c:v>2264877</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3525683</c:v>
+                  <c:v>1248152397</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>6045207</c:v>
+                  <c:v>2942139</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-1F21-483E-9B53-5576CF558DA3}"/>
+              <c16:uniqueId val="{00000003-8994-4B5A-A9DB-B8492F1E0B06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9003,11 +9217,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$8</c:f>
+              <c:f>Comparison!$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Heap Sort</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9023,62 +9237,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$4:$G$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$5:$A$10</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$8:$G$8</c:f>
+              <c:f>Comparison!$E$5:$E$10</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>383118</c:v>
+                  <c:v>10000066045</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1290735</c:v>
+                  <c:v>332768</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2264877</c:v>
+                  <c:v>1047503</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4829709</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15902520</c:v>
+                  <c:v>4996899593</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>27596964</c:v>
+                  <c:v>6233869</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-1F21-483E-9B53-5576CF558DA3}"/>
+              <c16:uniqueId val="{00000004-8994-4B5A-A9DB-B8492F1E0B06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9087,11 +9300,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$9</c:f>
+              <c:f>Comparison!$F$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Insertion Sort</c:v>
+                  <c:v>300000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9107,62 +9320,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$4:$G$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$5:$A$10</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$9:$G$9</c:f>
+              <c:f>Comparison!$F$5:$F$10</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>50126147</c:v>
+                  <c:v>90000391152</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>451707034</c:v>
+                  <c:v>932768</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1248152397</c:v>
+                  <c:v>3525683</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4996899593</c:v>
+                  <c:v>15902520</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>44960162813</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>125068299550</c:v>
+                  <c:v>20347429</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-1F21-483E-9B53-5576CF558DA3}"/>
+              <c16:uniqueId val="{00000005-8994-4B5A-A9DB-B8492F1E0B06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9171,11 +9383,11 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$10</c:f>
+              <c:f>Comparison!$G$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Merge Sort</c:v>
+                  <c:v>500000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9191,52 +9403,51 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$4:$G$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$5:$A$10</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$10:$G$10</c:f>
+              <c:f>Comparison!$G$5:$G$10</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>506975</c:v>
+                  <c:v>249999489560</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1684990</c:v>
+                  <c:v>1532768</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2942139</c:v>
+                  <c:v>6045207</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>6233869</c:v>
+                  <c:v>27596964</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>20347429</c:v>
+                  <c:v>125068299550</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>35177282</c:v>
@@ -9246,7 +9457,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-1F21-483E-9B53-5576CF558DA3}"/>
+              <c16:uniqueId val="{00000006-8994-4B5A-A9DB-B8492F1E0B06}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9651,15 +9862,92 @@
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparison!$B$4</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$11:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Radix Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Shaker Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$B$11:$B$15</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>309131</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>110097</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100019998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>75264350</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>560940</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-54EA-4DB5-98A7-69E235C42A85}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
           <c:idx val="1"/>
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$11</c:f>
+              <c:f>Comparison!$C$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Quick Sort</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9675,62 +9963,55 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$4:$G$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$11:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$11:$G$11</c:f>
+              <c:f>Comparison!$C$11:$C$15</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>309131</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1064575</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1064575</c:v>
+                  <c:v>390120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1788759</c:v>
+                  <c:v>900059998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3948979</c:v>
+                  <c:v>674834958</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14531101</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>26904195</c:v>
+                  <c:v>1985441</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-FFFF-4135-B03C-7A580E25AEF5}"/>
+              <c16:uniqueId val="{00000001-54EA-4DB5-98A7-69E235C42A85}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9739,11 +10020,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$12</c:f>
+              <c:f>Comparison!$D$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Radix Sort</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9759,62 +10040,55 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$4:$G$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$11:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$12:$G$12</c:f>
+              <c:f>Comparison!$D$11:$D$15</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>110097</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1788759</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>390120</c:v>
+                  <c:v>650120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>650120</c:v>
+                  <c:v>2500099998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>1300120</c:v>
+                  <c:v>1880513010</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>3900120</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>6500120</c:v>
+                  <c:v>3828031</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-FFFF-4135-B03C-7A580E25AEF5}"/>
+              <c16:uniqueId val="{00000003-54EA-4DB5-98A7-69E235C42A85}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9823,11 +10097,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$13</c:f>
+              <c:f>Comparison!$E$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Selection Sort</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9843,62 +10117,55 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$4:$G$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$11:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$13:$G$13</c:f>
+              <c:f>Comparison!$E$11:$E$15</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>100019998</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3948979</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>900059998</c:v>
+                  <c:v>1300120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2500099998</c:v>
+                  <c:v>10000199998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10000199998</c:v>
+                  <c:v>7484826744</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90000599998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>250000999998</c:v>
+                  <c:v>8344529</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-FFFF-4135-B03C-7A580E25AEF5}"/>
+              <c16:uniqueId val="{00000004-54EA-4DB5-98A7-69E235C42A85}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9907,11 +10174,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$14</c:f>
+              <c:f>Comparison!$F$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Shaker Sort</c:v>
+                  <c:v>300000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -9927,62 +10194,55 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$4:$G$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$11:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$14:$G$14</c:f>
+              <c:f>Comparison!$F$11:$F$15</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>75264350</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>14531101</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>674834958</c:v>
+                  <c:v>3900120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1880513010</c:v>
+                  <c:v>90000599998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>7484826744</c:v>
+                  <c:v>67311957498</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>67311957498</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>187697095158</c:v>
+                  <c:v>31787500</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-FFFF-4135-B03C-7A580E25AEF5}"/>
+              <c16:uniqueId val="{00000005-54EA-4DB5-98A7-69E235C42A85}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -9991,11 +10251,11 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$15</c:f>
+              <c:f>Comparison!$G$4</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Shell Sort</c:v>
+                  <c:v>500000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10011,54 +10271,47 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$4:$G$4</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$11:$A$15</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$15:$G$15</c:f>
+              <c:f>Comparison!$G$11:$G$15</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>560940</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>26904195</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1985441</c:v>
+                  <c:v>6500120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>3828031</c:v>
+                  <c:v>250000999998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>8344529</c:v>
+                  <c:v>187697095158</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>31787500</c:v>
-                </c:pt>
-                <c:pt idx="5">
                   <c:v>61559473</c:v>
                 </c:pt>
               </c:numCache>
@@ -10066,7 +10319,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-FFFF-4135-B03C-7A580E25AEF5}"/>
+              <c16:uniqueId val="{00000006-54EA-4DB5-98A7-69E235C42A85}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -10082,114 +10335,7 @@
         <c:overlap val="-27"/>
         <c:axId val="990035744"/>
         <c:axId val="990037664"/>
-        <c:extLst>
-          <c:ext xmlns:c15="http://schemas.microsoft.com/office/drawing/2012/chart" uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-            <c15:filteredBarSeries>
-              <c15:ser>
-                <c:idx val="0"/>
-                <c:order val="0"/>
-                <c:tx>
-                  <c:strRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Comparison!$A$4</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:strCache>
-                      <c:ptCount val="1"/>
-                      <c:pt idx="0">
-                        <c:v>Data size</c:v>
-                      </c:pt>
-                    </c:strCache>
-                  </c:strRef>
-                </c:tx>
-                <c:spPr>
-                  <a:solidFill>
-                    <a:schemeClr val="accent1"/>
-                  </a:solidFill>
-                  <a:ln>
-                    <a:noFill/>
-                  </a:ln>
-                  <a:effectLst/>
-                </c:spPr>
-                <c:invertIfNegative val="0"/>
-                <c:cat>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Comparison!$B$4:$G$4</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="6"/>
-                      <c:pt idx="0">
-                        <c:v>10000</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>30000</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>50000</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>100000</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>300000</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>500000</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:cat>
-                <c:val>
-                  <c:numRef>
-                    <c:extLst>
-                      <c:ext uri="{02D57815-91ED-43cb-92C2-25804820EDAC}">
-                        <c15:formulaRef>
-                          <c15:sqref>Comparison!$B$4:$G$4</c15:sqref>
-                        </c15:formulaRef>
-                      </c:ext>
-                    </c:extLst>
-                    <c:numCache>
-                      <c:formatCode>General</c:formatCode>
-                      <c:ptCount val="6"/>
-                      <c:pt idx="0">
-                        <c:v>10000</c:v>
-                      </c:pt>
-                      <c:pt idx="1">
-                        <c:v>30000</c:v>
-                      </c:pt>
-                      <c:pt idx="2">
-                        <c:v>50000</c:v>
-                      </c:pt>
-                      <c:pt idx="3">
-                        <c:v>100000</c:v>
-                      </c:pt>
-                      <c:pt idx="4">
-                        <c:v>300000</c:v>
-                      </c:pt>
-                      <c:pt idx="5">
-                        <c:v>500000</c:v>
-                      </c:pt>
-                    </c:numCache>
-                  </c:numRef>
-                </c:val>
-                <c:extLst>
-                  <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-                    <c16:uniqueId val="{00000000-FFFF-4135-B03C-7A580E25AEF5}"/>
-                  </c:ext>
-                </c:extLst>
-              </c15:ser>
-            </c15:filteredBarSeries>
-          </c:ext>
-        </c:extLst>
+        <c:extLst/>
       </c:barChart>
       <c:catAx>
         <c:axId val="990035744"/>
@@ -10585,11 +10731,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$20</c:f>
+              <c:f>Comparison!$B$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Bubble Sort</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10605,35 +10751,34 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$19:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$20:$A$25</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$20:$G$20</c:f>
+              <c:f>Comparison!$B$20:$B$25</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
@@ -10641,19 +10786,19 @@
                   <c:v>98706685</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>796183137</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1535873297</c:v>
+                  <c:v>83529</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3624496897</c:v>
+                  <c:v>396813</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>14630035632</c:v>
+                  <c:v>164326</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>26570836145</c:v>
+                  <c:v>424995</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10669,11 +10814,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$21</c:f>
+              <c:f>Comparison!$C$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Counting Sort</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10689,55 +10834,54 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$19:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$20:$A$25</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$21:$G$21</c:f>
+              <c:f>Comparison!$C$20:$C$25</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>40000</c:v>
+                  <c:v>796183137</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>120000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>200000</c:v>
+                  <c:v>250532</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>400000</c:v>
+                  <c:v>1329591</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1200000</c:v>
+                  <c:v>306838</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000000</c:v>
+                  <c:v>1373054</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10753,11 +10897,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$22</c:f>
+              <c:f>Comparison!$D$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Flash Sort</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10773,55 +10917,54 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$19:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$20:$A$25</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$22:$G$22</c:f>
+              <c:f>Comparison!$D$20:$D$25</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>83529</c:v>
+                  <c:v>1535873297</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>250532</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>417529</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>835023</c:v>
+                  <c:v>2333193</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2505034</c:v>
+                  <c:v>623226</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4175025</c:v>
+                  <c:v>2367677</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10837,11 +10980,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$23</c:f>
+              <c:f>Comparison!$E$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Heap Sort</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10857,55 +11000,54 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$19:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$20:$A$25</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$23:$G$23</c:f>
+              <c:f>Comparison!$E$20:$E$25</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>396813</c:v>
+                  <c:v>3624496897</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1329591</c:v>
+                  <c:v>400000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2333193</c:v>
+                  <c:v>835023</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4969320</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16322175</c:v>
+                  <c:v>743862</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>28268334</c:v>
+                  <c:v>4900830</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -10921,11 +11063,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$24</c:f>
+              <c:f>Comparison!$F$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Insertion Sort</c:v>
+                  <c:v>300000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -10941,55 +11083,54 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$19:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$20:$A$25</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$24:$G$24</c:f>
+              <c:f>Comparison!$F$20:$F$25</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>164326</c:v>
+                  <c:v>14630035632</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>306838</c:v>
+                  <c:v>1200000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>623226</c:v>
+                  <c:v>2505034</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>743862</c:v>
+                  <c:v>16322175</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>1362474</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1690026</c:v>
+                  <c:v>15650920</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -11005,11 +11146,11 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$25</c:f>
+              <c:f>Comparison!$G$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Merge Sort</c:v>
+                  <c:v>500000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11025,52 +11166,51 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$19:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$20:$A$25</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$25:$G$25</c:f>
+              <c:f>Comparison!$G$20:$G$25</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>424995</c:v>
+                  <c:v>26570836145</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1373054</c:v>
+                  <c:v>2000000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2367677</c:v>
+                  <c:v>4175025</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4900830</c:v>
+                  <c:v>28268334</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15650920</c:v>
+                  <c:v>1690026</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>26806893</c:v>
@@ -11510,15 +11650,92 @@
         <c:grouping val="clustered"/>
         <c:varyColors val="0"/>
         <c:ser>
-          <c:idx val="0"/>
+          <c:idx val="1"/>
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$26</c:f>
+              <c:f>Comparison!$B$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
+                  <c:v>10000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent2"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$26:$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
                   <c:v>Quick Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Radix Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Shaker Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$B$26:$B$30</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>302725</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>110097</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>100019998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>279818</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>279806</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000002-2B27-432A-94B5-055F2E6230E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparison!$C$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>30000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11534,146 +11751,55 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$19:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$26:$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$26:$G$26</c:f>
+              <c:f>Comparison!$C$26:$C$30</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>302725</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1054227</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1054227</c:v>
+                  <c:v>390120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1784119</c:v>
+                  <c:v>900059998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3579619</c:v>
+                  <c:v>959760</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11069303</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>18905233</c:v>
+                  <c:v>926244</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-4CF5-460D-8FD8-3AD55C5F2102}"/>
-            </c:ext>
-          </c:extLst>
-        </c:ser>
-        <c:ser>
-          <c:idx val="1"/>
-          <c:order val="1"/>
-          <c:tx>
-            <c:strRef>
-              <c:f>Comparison!$A$27</c:f>
-              <c:strCache>
-                <c:ptCount val="1"/>
-                <c:pt idx="0">
-                  <c:v>Radix Sort</c:v>
-                </c:pt>
-              </c:strCache>
-            </c:strRef>
-          </c:tx>
-          <c:spPr>
-            <a:solidFill>
-              <a:schemeClr val="accent2"/>
-            </a:solidFill>
-            <a:ln>
-              <a:noFill/>
-            </a:ln>
-            <a:effectLst/>
-          </c:spPr>
-          <c:invertIfNegative val="0"/>
-          <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$19:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>30000</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>50000</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>100000</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:cat>
-          <c:val>
-            <c:numRef>
-              <c:f>Comparison!$B$27:$G$27</c:f>
-              <c:numCache>
-                <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>110097</c:v>
-                </c:pt>
-                <c:pt idx="1">
-                  <c:v>390120</c:v>
-                </c:pt>
-                <c:pt idx="2">
-                  <c:v>650120</c:v>
-                </c:pt>
-                <c:pt idx="3">
-                  <c:v>1300120</c:v>
-                </c:pt>
-                <c:pt idx="4">
-                  <c:v>4500143</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>7500143</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
-          </c:val>
-          <c:extLst>
-            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-4CF5-460D-8FD8-3AD55C5F2102}"/>
+              <c16:uniqueId val="{00000001-2B27-432A-94B5-055F2E6230E1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11682,11 +11808,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$28</c:f>
+              <c:f>Comparison!$D$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Selection Sort</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11702,62 +11828,55 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$19:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$26:$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$28:$G$28</c:f>
+              <c:f>Comparison!$D$26:$D$30</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>100019998</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>1784119</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>900059998</c:v>
+                  <c:v>650120</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>2500099998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>10000199998</c:v>
+                  <c:v>1199868</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>90000599998</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>250000999998</c:v>
+                  <c:v>1543380</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-4CF5-460D-8FD8-3AD55C5F2102}"/>
+              <c16:uniqueId val="{00000003-2B27-432A-94B5-055F2E6230E1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11766,11 +11885,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$29</c:f>
+              <c:f>Comparison!$E$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Shaker Sort</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11786,62 +11905,55 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$19:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$26:$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$29:$G$29</c:f>
+              <c:f>Comparison!$E$26:$E$30</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>279818</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>3579619</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>959760</c:v>
+                  <c:v>1300120</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1199868</c:v>
+                  <c:v>10000199998</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>2799818</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>11999620</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>17999694</c:v>
+                  <c:v>3062589</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-4CF5-460D-8FD8-3AD55C5F2102}"/>
+              <c16:uniqueId val="{00000004-2B27-432A-94B5-055F2E6230E1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -11850,11 +11962,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$30</c:f>
+              <c:f>Comparison!$F$19</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Shell Sort</c:v>
+                  <c:v>300000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -11870,62 +11982,132 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$19:$G$19</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>10000</c:v>
+            <c:strRef>
+              <c:f>Comparison!$A$26:$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Radix Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Selection Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Shaker Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$30:$G$30</c:f>
+              <c:f>Comparison!$F$26:$F$30</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
-                <c:ptCount val="6"/>
-                <c:pt idx="0">
-                  <c:v>279806</c:v>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>11069303</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>926244</c:v>
+                  <c:v>4500143</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>1543380</c:v>
+                  <c:v>90000599998</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>3062589</c:v>
+                  <c:v>11999620</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>9816956</c:v>
-                </c:pt>
-                <c:pt idx="5">
-                  <c:v>16954347</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-4CF5-460D-8FD8-3AD55C5F2102}"/>
+              <c16:uniqueId val="{00000005-2B27-432A-94B5-055F2E6230E1}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:ser>
+          <c:idx val="5"/>
+          <c:order val="5"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>Comparison!$G$19</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>500000</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent6"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:cat>
+            <c:strRef>
+              <c:f>Comparison!$A$26:$A$30</c:f>
+              <c:strCache>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>Quick Sort</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>Radix Sort</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>Selection Sort</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>Shaker Sort</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>Shell Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:cat>
+          <c:val>
+            <c:numRef>
+              <c:f>Comparison!$G$26:$G$30</c:f>
+              <c:numCache>
+                <c:formatCode>#,##0</c:formatCode>
+                <c:ptCount val="5"/>
+                <c:pt idx="0">
+                  <c:v>18905233</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>7500143</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>250000999998</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>17999694</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>16954347</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000006-2B27-432A-94B5-055F2E6230E1}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12324,11 +12506,11 @@
           <c:order val="0"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$35</c:f>
+              <c:f>Comparison!$B$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Bubble Sort</c:v>
+                  <c:v>10000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -12344,35 +12526,34 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$34:$G$34</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$35:$A$40</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$35:$G$35</c:f>
+              <c:f>Comparison!$B$35:$B$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
@@ -12380,26 +12561,26 @@
                   <c:v>20001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>60001</c:v>
+                  <c:v>40000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>100001</c:v>
+                  <c:v>83514</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>200001</c:v>
+                  <c:v>396864</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>600001</c:v>
+                  <c:v>29998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1000001</c:v>
+                  <c:v>396235</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000000-D3E5-4D28-B469-B745F03AF503}"/>
+              <c16:uniqueId val="{00000000-46A2-4ECB-BF49-A507CA43BED2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12408,11 +12589,11 @@
           <c:order val="1"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$36</c:f>
+              <c:f>Comparison!$C$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Counting Sort</c:v>
+                  <c:v>30000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -12428,62 +12609,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$34:$G$34</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$35:$A$40</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$36:$G$36</c:f>
+              <c:f>Comparison!$C$35:$C$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>40000</c:v>
+                  <c:v>60001</c:v>
                 </c:pt>
                 <c:pt idx="1">
                   <c:v>120000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>200000</c:v>
+                  <c:v>250514</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>400000</c:v>
+                  <c:v>1329555</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>1200000</c:v>
+                  <c:v>89998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>2000000</c:v>
+                  <c:v>1302187</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000001-D3E5-4D28-B469-B745F03AF503}"/>
+              <c16:uniqueId val="{00000001-46A2-4ECB-BF49-A507CA43BED2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12492,11 +12672,11 @@
           <c:order val="2"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$37</c:f>
+              <c:f>Comparison!$D$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Flash Sort</c:v>
+                  <c:v>50000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -12512,62 +12692,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$34:$G$34</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$35:$A$40</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$37:$G$37</c:f>
+              <c:f>Comparison!$D$35:$D$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>83514</c:v>
+                  <c:v>100001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>250514</c:v>
+                  <c:v>200000</c:v>
                 </c:pt>
                 <c:pt idx="2">
                   <c:v>417514</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>835014</c:v>
+                  <c:v>2333214</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>2505014</c:v>
+                  <c:v>149998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>4175014</c:v>
+                  <c:v>2270875</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000002-D3E5-4D28-B469-B745F03AF503}"/>
+              <c16:uniqueId val="{00000002-46A2-4ECB-BF49-A507CA43BED2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12576,11 +12755,11 @@
           <c:order val="3"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$38</c:f>
+              <c:f>Comparison!$E$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Heap Sort</c:v>
+                  <c:v>100000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -12596,62 +12775,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$34:$G$34</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$35:$A$40</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$38:$G$38</c:f>
+              <c:f>Comparison!$E$35:$E$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>396864</c:v>
+                  <c:v>200001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1329555</c:v>
+                  <c:v>400000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2333214</c:v>
+                  <c:v>835014</c:v>
                 </c:pt>
                 <c:pt idx="3">
                   <c:v>4969323</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>16322181</c:v>
+                  <c:v>299998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>28268367</c:v>
+                  <c:v>4791755</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000003-D3E5-4D28-B469-B745F03AF503}"/>
+              <c16:uniqueId val="{00000003-46A2-4ECB-BF49-A507CA43BED2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12660,11 +12838,11 @@
           <c:order val="4"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$39</c:f>
+              <c:f>Comparison!$F$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Insertion Sort</c:v>
+                  <c:v>300000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -12680,62 +12858,61 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$34:$G$34</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$35:$A$40</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$39:$G$39</c:f>
+              <c:f>Comparison!$F$35:$F$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>29998</c:v>
+                  <c:v>600001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>89998</c:v>
+                  <c:v>1200000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>149998</c:v>
+                  <c:v>2505014</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>299998</c:v>
+                  <c:v>16322181</c:v>
                 </c:pt>
                 <c:pt idx="4">
                   <c:v>899998</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>1499998</c:v>
+                  <c:v>15548683</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000004-D3E5-4D28-B469-B745F03AF503}"/>
+              <c16:uniqueId val="{00000004-46A2-4ECB-BF49-A507CA43BED2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -12744,11 +12921,11 @@
           <c:order val="5"/>
           <c:tx>
             <c:strRef>
-              <c:f>Comparison!$A$40</c:f>
+              <c:f>Comparison!$G$34</c:f>
               <c:strCache>
                 <c:ptCount val="1"/>
                 <c:pt idx="0">
-                  <c:v>Merge Sort</c:v>
+                  <c:v>500000</c:v>
                 </c:pt>
               </c:strCache>
             </c:strRef>
@@ -12764,52 +12941,51 @@
           </c:spPr>
           <c:invertIfNegative val="0"/>
           <c:cat>
-            <c:numRef>
-              <c:f>Comparison!$B$34:$G$34</c:f>
-              <c:numCache>
-                <c:formatCode>General</c:formatCode>
+            <c:strRef>
+              <c:f>Comparison!$A$35:$A$40</c:f>
+              <c:strCache>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>10000</c:v>
+                  <c:v>Bubble Sort</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>30000</c:v>
+                  <c:v>Counting Sort</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>50000</c:v>
+                  <c:v>Flash Sort</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>100000</c:v>
+                  <c:v>Heap Sort</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>300000</c:v>
+                  <c:v>Insertion Sort</c:v>
                 </c:pt>
                 <c:pt idx="5">
-                  <c:v>500000</c:v>
-                </c:pt>
-              </c:numCache>
-            </c:numRef>
+                  <c:v>Merge Sort</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
           </c:cat>
           <c:val>
             <c:numRef>
-              <c:f>Comparison!$B$40:$G$40</c:f>
+              <c:f>Comparison!$G$35:$G$40</c:f>
               <c:numCache>
                 <c:formatCode>#,##0</c:formatCode>
                 <c:ptCount val="6"/>
                 <c:pt idx="0">
-                  <c:v>396235</c:v>
+                  <c:v>1000001</c:v>
                 </c:pt>
                 <c:pt idx="1">
-                  <c:v>1302187</c:v>
+                  <c:v>2000000</c:v>
                 </c:pt>
                 <c:pt idx="2">
-                  <c:v>2270875</c:v>
+                  <c:v>4175014</c:v>
                 </c:pt>
                 <c:pt idx="3">
-                  <c:v>4791755</c:v>
+                  <c:v>28268367</c:v>
                 </c:pt>
                 <c:pt idx="4">
-                  <c:v>15548683</c:v>
+                  <c:v>1499998</c:v>
                 </c:pt>
                 <c:pt idx="5">
                   <c:v>26734635</c:v>
@@ -12819,7 +12995,7 @@
           </c:val>
           <c:extLst>
             <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
-              <c16:uniqueId val="{00000005-D3E5-4D28-B469-B745F03AF503}"/>
+              <c16:uniqueId val="{00000005-46A2-4ECB-BF49-A507CA43BED2}"/>
             </c:ext>
           </c:extLst>
         </c:ser>
@@ -20125,15 +20301,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>544285</xdr:colOff>
-      <xdr:row>47</xdr:row>
-      <xdr:rowOff>91168</xdr:rowOff>
+      <xdr:colOff>491369</xdr:colOff>
+      <xdr:row>46</xdr:row>
+      <xdr:rowOff>161724</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>26</xdr:col>
-      <xdr:colOff>245871</xdr:colOff>
+      <xdr:colOff>192955</xdr:colOff>
       <xdr:row>60</xdr:row>
-      <xdr:rowOff>170646</xdr:rowOff>
+      <xdr:rowOff>47174</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -20159,10 +20335,6 @@
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -23540,7 +23712,7 @@
     </row>
     <row r="49" spans="1:7" ht="26.25" x14ac:dyDescent="0.25">
       <c r="A49" s="15" t="s">
-        <v>20</v>
+        <v>23</v>
       </c>
       <c r="B49" s="15"/>
       <c r="C49" s="15"/>

--- a/Report/Measuring.xlsx
+++ b/Report/Measuring.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="26529"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="20373"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://studenthcmusedu-my.sharepoint.com/personal/22127275_student_hcmus_edu_vn/Documents/Programming/DSA/Lab3_Sorting/Report/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Admin\Documents\FirstYear\HKIII\Data Structures and Algorithms\Practice\Lab03\Lab3_Sorting\Report\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="2317" documentId="8_{DA9940A0-0571-4566-AD57-949AA40DBC63}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4698F8FA-A5FA-4619-83BC-E7B2AAD6D1C2}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D158BD40-F46C-4A0E-8C21-38BCBA120FD5}" xr6:coauthVersionLast="36" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="1" xr2:uid="{00802968-0738-4320-9C05-4460BE5590E3}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="16440" activeTab="2" xr2:uid="{00802968-0738-4320-9C05-4460BE5590E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="2" r:id="rId1"/>
@@ -27,10 +27,10 @@
         <xcalcf:feature name="microsoft.com:RD"/>
         <xcalcf:feature name="microsoft.com:Single"/>
         <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
         <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
         <xcalcf:feature name="microsoft.com:LET_WF"/>
-        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
-        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
       </xcalcf:calcFeatures>
     </ext>
   </extLst>
@@ -20049,15 +20049,15 @@
   <xdr:twoCellAnchor>
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>168088</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>31537</xdr:rowOff>
+      <xdr:colOff>212185</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>190287</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>16</xdr:col>
-      <xdr:colOff>482029</xdr:colOff>
+      <xdr:colOff>526126</xdr:colOff>
       <xdr:row>15</xdr:row>
-      <xdr:rowOff>111478</xdr:rowOff>
+      <xdr:rowOff>76200</xdr:rowOff>
     </xdr:to>
     <xdr:graphicFrame macro="">
       <xdr:nvGraphicFramePr>
@@ -22804,6 +22804,27 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="A2:M2"/>
+    <mergeCell ref="B3:C3"/>
+    <mergeCell ref="D3:E3"/>
+    <mergeCell ref="F3:G3"/>
+    <mergeCell ref="H3:I3"/>
+    <mergeCell ref="J3:K3"/>
+    <mergeCell ref="L3:M3"/>
+    <mergeCell ref="A52:M52"/>
+    <mergeCell ref="B53:C53"/>
+    <mergeCell ref="D53:E53"/>
+    <mergeCell ref="F53:G53"/>
+    <mergeCell ref="H53:I53"/>
+    <mergeCell ref="J53:K53"/>
+    <mergeCell ref="L53:M53"/>
+    <mergeCell ref="A35:M35"/>
+    <mergeCell ref="B36:C36"/>
+    <mergeCell ref="D36:E36"/>
+    <mergeCell ref="F36:G36"/>
+    <mergeCell ref="H36:I36"/>
+    <mergeCell ref="J36:K36"/>
+    <mergeCell ref="L36:M36"/>
     <mergeCell ref="A18:M18"/>
     <mergeCell ref="B19:C19"/>
     <mergeCell ref="D19:E19"/>
@@ -22811,27 +22832,6 @@
     <mergeCell ref="H19:I19"/>
     <mergeCell ref="J19:K19"/>
     <mergeCell ref="L19:M19"/>
-    <mergeCell ref="A35:M35"/>
-    <mergeCell ref="B36:C36"/>
-    <mergeCell ref="D36:E36"/>
-    <mergeCell ref="F36:G36"/>
-    <mergeCell ref="H36:I36"/>
-    <mergeCell ref="J36:K36"/>
-    <mergeCell ref="L36:M36"/>
-    <mergeCell ref="A52:M52"/>
-    <mergeCell ref="B53:C53"/>
-    <mergeCell ref="D53:E53"/>
-    <mergeCell ref="F53:G53"/>
-    <mergeCell ref="H53:I53"/>
-    <mergeCell ref="J53:K53"/>
-    <mergeCell ref="L53:M53"/>
-    <mergeCell ref="A2:M2"/>
-    <mergeCell ref="B3:C3"/>
-    <mergeCell ref="D3:E3"/>
-    <mergeCell ref="F3:G3"/>
-    <mergeCell ref="H3:I3"/>
-    <mergeCell ref="J3:K3"/>
-    <mergeCell ref="L3:M3"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" r:id="rId1"/>
